--- a/research/traditional_assets/database/data/turkey/turkey_entertainment.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_entertainment.xlsx
@@ -1659,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1796,22 +1796,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1510152868139058</v>
+        <v>0.150671498596871</v>
       </c>
       <c r="C2">
-        <v>60.21723438944374</v>
+        <v>59.81290158884545</v>
       </c>
       <c r="D2">
-        <v>60.20623438944374</v>
+        <v>60.40360158884545</v>
       </c>
       <c r="E2">
-        <v>-1.77</v>
+        <v>-1.1683</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.6017</v>
       </c>
       <c r="G2">
         <v>0.011</v>
@@ -1832,28 +1832,28 @@
         <v>1.525</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03026551</v>
       </c>
       <c r="N2">
-        <v>1.525</v>
+        <v>1.49473449</v>
       </c>
       <c r="O2">
-        <v>0.38125</v>
+        <v>0.3736836225</v>
       </c>
       <c r="P2">
-        <v>1.14375</v>
+        <v>1.1210508675</v>
       </c>
       <c r="Q2">
-        <v>1.97875</v>
+        <v>1.9560508675</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1510152868139058</v>
+        <v>0.1518123723200717</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.025220663724927</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>50.38738815238865</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1878,22 +1878,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.150671498596871</v>
+        <v>0.1503277103798363</v>
       </c>
       <c r="C3">
-        <v>59.81290158884545</v>
+        <v>59.40986705676055</v>
       </c>
       <c r="D3">
-        <v>60.40360158884545</v>
+        <v>60.60226705676055</v>
       </c>
       <c r="E3">
-        <v>-1.1683</v>
+        <v>-0.5666</v>
       </c>
       <c r="F3">
-        <v>0.6017</v>
+        <v>1.2034</v>
       </c>
       <c r="G3">
         <v>0.011</v>
@@ -1914,28 +1914,28 @@
         <v>1.525</v>
       </c>
       <c r="M3">
-        <v>0.03026551</v>
+        <v>0.06053102</v>
       </c>
       <c r="N3">
-        <v>1.49473449</v>
+        <v>1.46446898</v>
       </c>
       <c r="O3">
-        <v>0.3736836225</v>
+        <v>0.366117245</v>
       </c>
       <c r="P3">
-        <v>1.1210508675</v>
+        <v>1.098351735</v>
       </c>
       <c r="Q3">
-        <v>1.9560508675</v>
+        <v>1.933351735</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1518123723200717</v>
+        <v>0.152625724877384</v>
       </c>
       <c r="T3">
-        <v>1.025220663724927</v>
+        <v>1.033086404585177</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>50.38738815238865</v>
+        <v>25.19369407619432</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1960,22 +1960,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1503277103798363</v>
+        <v>0.1499839221628015</v>
       </c>
       <c r="C4">
-        <v>59.40986705676055</v>
+        <v>59.00814364534736</v>
       </c>
       <c r="D4">
-        <v>60.60226705676055</v>
+        <v>60.80224364534736</v>
       </c>
       <c r="E4">
-        <v>-0.5666</v>
+        <v>0.03509999999999991</v>
       </c>
       <c r="F4">
-        <v>1.2034</v>
+        <v>1.8051</v>
       </c>
       <c r="G4">
         <v>0.011</v>
@@ -1996,28 +1996,28 @@
         <v>1.525</v>
       </c>
       <c r="M4">
-        <v>0.06053102</v>
+        <v>0.09079652999999999</v>
       </c>
       <c r="N4">
-        <v>1.46446898</v>
+        <v>1.43420347</v>
       </c>
       <c r="O4">
-        <v>0.366117245</v>
+        <v>0.3585508675</v>
       </c>
       <c r="P4">
-        <v>1.098351735</v>
+        <v>1.0756526025</v>
       </c>
       <c r="Q4">
-        <v>1.933351735</v>
+        <v>1.9106526025</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.152625724877384</v>
+        <v>0.153455847590517</v>
       </c>
       <c r="T4">
-        <v>1.033086404585177</v>
+        <v>1.041114325669349</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>25.19369407619432</v>
+        <v>16.79579605079622</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2042,22 +2042,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1499839221628015</v>
+        <v>0.1496851339457667</v>
       </c>
       <c r="C5">
-        <v>59.00814364534736</v>
+        <v>58.58131942670787</v>
       </c>
       <c r="D5">
-        <v>60.80224364534736</v>
+        <v>60.97711942670787</v>
       </c>
       <c r="E5">
-        <v>0.03509999999999991</v>
+        <v>0.6368</v>
       </c>
       <c r="F5">
-        <v>1.8051</v>
+        <v>2.4068</v>
       </c>
       <c r="G5">
         <v>0.011</v>
@@ -2078,45 +2078,45 @@
         <v>1.525</v>
       </c>
       <c r="M5">
-        <v>0.09079652999999999</v>
+        <v>0.12467224</v>
       </c>
       <c r="N5">
-        <v>1.43420347</v>
+        <v>1.40032776</v>
       </c>
       <c r="O5">
-        <v>0.3585508675</v>
+        <v>0.35008194</v>
       </c>
       <c r="P5">
-        <v>1.0756526025</v>
+        <v>1.05024582</v>
       </c>
       <c r="Q5">
-        <v>1.9106526025</v>
+        <v>1.88524582</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.153455847590517</v>
+        <v>0.1543032645268403</v>
       </c>
       <c r="T5">
-        <v>1.041114325669349</v>
+        <v>1.049309495109441</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>16.79579605079622</v>
+        <v>12.2320734752179</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2124,22 +2124,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1496851339457667</v>
+        <v>0.1494163457287319</v>
       </c>
       <c r="C6">
-        <v>58.58131942670787</v>
+        <v>58.13779843886422</v>
       </c>
       <c r="D6">
-        <v>60.97711942670787</v>
+        <v>61.13529843886421</v>
       </c>
       <c r="E6">
-        <v>0.6368</v>
+        <v>1.2385</v>
       </c>
       <c r="F6">
-        <v>2.4068</v>
+        <v>3.0085</v>
       </c>
       <c r="G6">
         <v>0.011</v>
@@ -2160,45 +2160,45 @@
         <v>1.525</v>
       </c>
       <c r="M6">
-        <v>0.12467224</v>
+        <v>0.16095475</v>
       </c>
       <c r="N6">
-        <v>1.40032776</v>
+        <v>1.36404525</v>
       </c>
       <c r="O6">
-        <v>0.35008194</v>
+        <v>0.3410113125</v>
       </c>
       <c r="P6">
-        <v>1.05024582</v>
+        <v>1.0230339375</v>
       </c>
       <c r="Q6">
-        <v>1.88524582</v>
+        <v>1.8580339375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1543032645268403</v>
+        <v>0.1551685218197179</v>
       </c>
       <c r="T6">
-        <v>1.049309495109441</v>
+        <v>1.057677194432483</v>
       </c>
       <c r="U6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>12.2320734752179</v>
+        <v>9.474712613327659</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2206,22 +2206,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1494163457287319</v>
+        <v>0.1490965575116972</v>
       </c>
       <c r="C7">
-        <v>58.13779843886422</v>
+        <v>57.72536271404044</v>
       </c>
       <c r="D7">
-        <v>61.13529843886421</v>
+        <v>61.32456271404044</v>
       </c>
       <c r="E7">
-        <v>1.2385</v>
+        <v>1.8402</v>
       </c>
       <c r="F7">
-        <v>3.0085</v>
+        <v>3.6102</v>
       </c>
       <c r="G7">
         <v>0.011</v>
@@ -2242,28 +2242,28 @@
         <v>1.525</v>
       </c>
       <c r="M7">
-        <v>0.16095475</v>
+        <v>0.1931457</v>
       </c>
       <c r="N7">
-        <v>1.36404525</v>
+        <v>1.3318543</v>
       </c>
       <c r="O7">
-        <v>0.3410113125</v>
+        <v>0.332963575</v>
       </c>
       <c r="P7">
-        <v>1.0230339375</v>
+        <v>0.9988907249999999</v>
       </c>
       <c r="Q7">
-        <v>1.8580339375</v>
+        <v>1.833890725</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1551685218197179</v>
+        <v>0.1560521888422311</v>
       </c>
       <c r="T7">
-        <v>1.057677194432483</v>
+        <v>1.066222929911334</v>
       </c>
       <c r="U7">
         <v>0.0535</v>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>9.474712613327659</v>
+        <v>7.895593844439714</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2288,22 +2288,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1490965575116972</v>
+        <v>0.1488187692946625</v>
       </c>
       <c r="C8">
-        <v>57.72536271404044</v>
+        <v>57.28902326972756</v>
       </c>
       <c r="D8">
-        <v>61.32456271404044</v>
+        <v>61.48992326972756</v>
       </c>
       <c r="E8">
-        <v>1.8402</v>
+        <v>2.4419</v>
       </c>
       <c r="F8">
-        <v>3.6102</v>
+        <v>4.2119</v>
       </c>
       <c r="G8">
         <v>0.011</v>
@@ -2324,45 +2324,45 @@
         <v>1.525</v>
       </c>
       <c r="M8">
-        <v>0.1931457</v>
+        <v>0.22870617</v>
       </c>
       <c r="N8">
-        <v>1.3318543</v>
+        <v>1.29629383</v>
       </c>
       <c r="O8">
-        <v>0.332963575</v>
+        <v>0.3240734575</v>
       </c>
       <c r="P8">
-        <v>0.9988907249999999</v>
+        <v>0.9722203725</v>
       </c>
       <c r="Q8">
-        <v>1.833890725</v>
+        <v>1.8072203725</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1560521888422311</v>
+        <v>0.1569548594566263</v>
       </c>
       <c r="T8">
-        <v>1.066222929911334</v>
+        <v>1.074952444647795</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>7.895593844439715</v>
+        <v>6.667944288516571</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2370,22 +2370,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1488187692946624</v>
+        <v>0.1485649810776277</v>
       </c>
       <c r="C9">
-        <v>57.28902326972758</v>
+        <v>56.83917867639028</v>
       </c>
       <c r="D9">
-        <v>61.48992326972758</v>
+        <v>61.64177867639027</v>
       </c>
       <c r="E9">
-        <v>2.441900000000001</v>
+        <v>3.0436</v>
       </c>
       <c r="F9">
-        <v>4.211900000000001</v>
+        <v>4.8136</v>
       </c>
       <c r="G9">
         <v>0.011</v>
@@ -2406,45 +2406,45 @@
         <v>1.525</v>
       </c>
       <c r="M9">
-        <v>0.22870617</v>
+        <v>0.26619208</v>
       </c>
       <c r="N9">
-        <v>1.29629383</v>
+        <v>1.25880792</v>
       </c>
       <c r="O9">
-        <v>0.3240734574999999</v>
+        <v>0.31470198</v>
       </c>
       <c r="P9">
-        <v>0.9722203724999998</v>
+        <v>0.94410594</v>
       </c>
       <c r="Q9">
-        <v>1.8072203725</v>
+        <v>1.77910594</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1569548594566263</v>
+        <v>0.1578771533452475</v>
       </c>
       <c r="T9">
-        <v>1.074952444647795</v>
+        <v>1.083871731443744</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.667944288516569</v>
+        <v>5.728945804848889</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2452,22 +2452,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1485649810776277</v>
+        <v>0.1482586928605929</v>
       </c>
       <c r="C10">
-        <v>56.83917867639028</v>
+        <v>56.42174952699865</v>
       </c>
       <c r="D10">
-        <v>61.64177867639027</v>
+        <v>61.82604952699865</v>
       </c>
       <c r="E10">
-        <v>3.0436</v>
+        <v>3.6453</v>
       </c>
       <c r="F10">
-        <v>4.8136</v>
+        <v>5.4153</v>
       </c>
       <c r="G10">
         <v>0.011</v>
@@ -2488,28 +2488,28 @@
         <v>1.525</v>
       </c>
       <c r="M10">
-        <v>0.26619208</v>
+        <v>0.29946609</v>
       </c>
       <c r="N10">
-        <v>1.25880792</v>
+        <v>1.22553391</v>
       </c>
       <c r="O10">
-        <v>0.31470198</v>
+        <v>0.3063834774999999</v>
       </c>
       <c r="P10">
-        <v>0.94410594</v>
+        <v>0.9191504324999998</v>
       </c>
       <c r="Q10">
-        <v>1.77910594</v>
+        <v>1.7541504325</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1578771533452475</v>
+        <v>0.158819717429223</v>
       </c>
       <c r="T10">
-        <v>1.083871731443744</v>
+        <v>1.092987046520923</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.728945804848889</v>
+        <v>5.092396270976789</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2534,22 +2534,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1482586928605929</v>
+        <v>0.1479524046435581</v>
       </c>
       <c r="C11">
-        <v>56.42174952699865</v>
+        <v>56.00542539300987</v>
       </c>
       <c r="D11">
-        <v>61.82604952699865</v>
+        <v>62.01142539300987</v>
       </c>
       <c r="E11">
-        <v>3.6453</v>
+        <v>4.247</v>
       </c>
       <c r="F11">
-        <v>5.4153</v>
+        <v>6.016999999999999</v>
       </c>
       <c r="G11">
         <v>0.011</v>
@@ -2570,28 +2570,28 @@
         <v>1.525</v>
       </c>
       <c r="M11">
-        <v>0.29946609</v>
+        <v>0.3327401</v>
       </c>
       <c r="N11">
-        <v>1.22553391</v>
+        <v>1.1922599</v>
       </c>
       <c r="O11">
-        <v>0.3063834774999999</v>
+        <v>0.298064975</v>
       </c>
       <c r="P11">
-        <v>0.9191504324999998</v>
+        <v>0.8941949249999999</v>
       </c>
       <c r="Q11">
-        <v>1.7541504325</v>
+        <v>1.729194925</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.158819717429223</v>
+        <v>0.1597832273817313</v>
       </c>
       <c r="T11">
-        <v>1.092987046520923</v>
+        <v>1.102304924155373</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.092396270976789</v>
+        <v>4.583156643879111</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2616,22 +2616,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1479524046435581</v>
+        <v>0.1481411164265234</v>
       </c>
       <c r="C12">
-        <v>56.00542539300987</v>
+        <v>55.28937949706165</v>
       </c>
       <c r="D12">
-        <v>62.01142539300987</v>
+        <v>61.89707949706164</v>
       </c>
       <c r="E12">
-        <v>4.247</v>
+        <v>4.848700000000001</v>
       </c>
       <c r="F12">
-        <v>6.017</v>
+        <v>6.6187</v>
       </c>
       <c r="G12">
         <v>0.011</v>
@@ -2652,45 +2652,45 @@
         <v>1.525</v>
       </c>
       <c r="M12">
-        <v>0.3327401</v>
+        <v>0.40572631</v>
       </c>
       <c r="N12">
-        <v>1.1922599</v>
+        <v>1.11927369</v>
       </c>
       <c r="O12">
-        <v>0.298064975</v>
+        <v>0.2798184225</v>
       </c>
       <c r="P12">
-        <v>0.8941949249999999</v>
+        <v>0.8394552675</v>
       </c>
       <c r="Q12">
-        <v>1.729194925</v>
+        <v>1.6744552675</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1597832273817313</v>
+        <v>0.1607683892432847</v>
       </c>
       <c r="T12">
-        <v>1.102304924155373</v>
+        <v>1.111832192298462</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.041475</v>
+        <v>0.045975</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.583156643879111</v>
+        <v>3.758691419346209</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2698,22 +2698,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1481411164265234</v>
+        <v>0.1481318282094886</v>
       </c>
       <c r="C13">
-        <v>55.28937949706165</v>
+        <v>54.69329762700469</v>
       </c>
       <c r="D13">
-        <v>61.89707949706164</v>
+        <v>61.90269762700468</v>
       </c>
       <c r="E13">
-        <v>4.848700000000001</v>
+        <v>5.4504</v>
       </c>
       <c r="F13">
-        <v>6.6187</v>
+        <v>7.2204</v>
       </c>
       <c r="G13">
         <v>0.011</v>
@@ -2734,45 +2734,45 @@
         <v>1.525</v>
       </c>
       <c r="M13">
-        <v>0.40572631</v>
+        <v>0.46282764</v>
       </c>
       <c r="N13">
-        <v>1.11927369</v>
+        <v>1.06217236</v>
       </c>
       <c r="O13">
-        <v>0.2798184225</v>
+        <v>0.26554309</v>
       </c>
       <c r="P13">
-        <v>0.8394552675</v>
+        <v>0.7966292699999999</v>
       </c>
       <c r="Q13">
-        <v>1.6744552675</v>
+        <v>1.63162927</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1607683892432847</v>
+        <v>0.1617759411471461</v>
       </c>
       <c r="T13">
-        <v>1.111832192298462</v>
+        <v>1.121575989262984</v>
       </c>
       <c r="U13">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.758691419346209</v>
+        <v>3.294963109809085</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2780,22 +2780,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1481318282094886</v>
+        <v>0.1478915399924538</v>
       </c>
       <c r="C14">
-        <v>54.69329762700469</v>
+        <v>54.23729519257706</v>
       </c>
       <c r="D14">
-        <v>61.90269762700468</v>
+        <v>62.04839519257705</v>
       </c>
       <c r="E14">
-        <v>5.4504</v>
+        <v>6.052100000000001</v>
       </c>
       <c r="F14">
-        <v>7.2204</v>
+        <v>7.822100000000001</v>
       </c>
       <c r="G14">
         <v>0.011</v>
@@ -2816,28 +2816,28 @@
         <v>1.525</v>
       </c>
       <c r="M14">
-        <v>0.46282764</v>
+        <v>0.5013966100000001</v>
       </c>
       <c r="N14">
-        <v>1.06217236</v>
+        <v>1.02360339</v>
       </c>
       <c r="O14">
-        <v>0.26554309</v>
+        <v>0.2559008475</v>
       </c>
       <c r="P14">
-        <v>0.7966292699999999</v>
+        <v>0.7677025424999999</v>
       </c>
       <c r="Q14">
-        <v>1.63162927</v>
+        <v>1.6027025425</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1617759411471461</v>
+        <v>0.16280665516374</v>
       </c>
       <c r="T14">
-        <v>1.121575989262984</v>
+        <v>1.131543781560024</v>
       </c>
       <c r="U14">
         <v>0.0641</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>3.294963109809085</v>
+        <v>3.04150440905454</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2862,22 +2862,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1478915399924538</v>
+        <v>0.1484702517754191</v>
       </c>
       <c r="C15">
-        <v>54.23729519257706</v>
+        <v>53.28585282036029</v>
       </c>
       <c r="D15">
-        <v>62.04839519257705</v>
+        <v>61.69865282036029</v>
       </c>
       <c r="E15">
-        <v>6.052100000000001</v>
+        <v>6.653800000000002</v>
       </c>
       <c r="F15">
-        <v>7.822100000000001</v>
+        <v>8.423800000000002</v>
       </c>
       <c r="G15">
         <v>0.011</v>
@@ -2898,45 +2898,45 @@
         <v>1.525</v>
       </c>
       <c r="M15">
-        <v>0.5013966100000001</v>
+        <v>0.6056712200000002</v>
       </c>
       <c r="N15">
-        <v>1.02360339</v>
+        <v>0.9193287799999997</v>
       </c>
       <c r="O15">
-        <v>0.2559008475</v>
+        <v>0.2298321949999999</v>
       </c>
       <c r="P15">
-        <v>0.7677025424999999</v>
+        <v>0.6894965849999998</v>
       </c>
       <c r="Q15">
-        <v>1.6027025425</v>
+        <v>1.524496585</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.16280665516374</v>
+        <v>0.1638613392737431</v>
       </c>
       <c r="T15">
-        <v>1.131543781560024</v>
+        <v>1.141743382980252</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.04150440905454</v>
+        <v>2.517867697263211</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2944,22 +2944,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1484702517754191</v>
+        <v>0.1487272135583843</v>
       </c>
       <c r="C16">
-        <v>53.28585282036029</v>
+        <v>52.53011973924244</v>
       </c>
       <c r="D16">
-        <v>61.69865282036029</v>
+        <v>61.54461973924244</v>
       </c>
       <c r="E16">
-        <v>6.653800000000002</v>
+        <v>7.255500000000001</v>
       </c>
       <c r="F16">
-        <v>8.423800000000002</v>
+        <v>9.025500000000001</v>
       </c>
       <c r="G16">
         <v>0.011</v>
@@ -2980,45 +2980,45 @@
         <v>1.525</v>
       </c>
       <c r="M16">
-        <v>0.6056712200000002</v>
+        <v>0.6841329000000002</v>
       </c>
       <c r="N16">
-        <v>0.9193287799999997</v>
+        <v>0.8408670999999998</v>
       </c>
       <c r="O16">
-        <v>0.2298321949999999</v>
+        <v>0.2102167749999999</v>
       </c>
       <c r="P16">
-        <v>0.6894965849999998</v>
+        <v>0.6306503249999998</v>
       </c>
       <c r="Q16">
-        <v>1.524496585</v>
+        <v>1.465650325</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1638613392737431</v>
+        <v>0.1649408394804521</v>
       </c>
       <c r="T16">
-        <v>1.141743382980252</v>
+        <v>1.152182975022132</v>
       </c>
       <c r="U16">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.517867697263211</v>
+        <v>2.229099053707254</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3026,22 +3026,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1487272135583843</v>
+        <v>0.1485746753413495</v>
       </c>
       <c r="C17">
-        <v>52.53011973924244</v>
+        <v>52.01976429014397</v>
       </c>
       <c r="D17">
-        <v>61.54461973924244</v>
+        <v>61.63596429014397</v>
       </c>
       <c r="E17">
-        <v>7.2555</v>
+        <v>7.857200000000001</v>
       </c>
       <c r="F17">
-        <v>9.025499999999999</v>
+        <v>9.6272</v>
       </c>
       <c r="G17">
         <v>0.011</v>
@@ -3062,28 +3062,28 @@
         <v>1.525</v>
       </c>
       <c r="M17">
-        <v>0.6841329</v>
+        <v>0.7297417600000001</v>
       </c>
       <c r="N17">
-        <v>0.8408670999999999</v>
+        <v>0.7952582399999998</v>
       </c>
       <c r="O17">
-        <v>0.210216775</v>
+        <v>0.1988145599999999</v>
       </c>
       <c r="P17">
-        <v>0.630650325</v>
+        <v>0.5964436799999998</v>
       </c>
       <c r="Q17">
-        <v>1.465650325</v>
+        <v>1.43144368</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1649408394804521</v>
+        <v>0.1660460420730352</v>
       </c>
       <c r="T17">
-        <v>1.152182975022132</v>
+        <v>1.162871128779294</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.229099053707254</v>
+        <v>2.089780362850551</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3108,22 +3108,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1485746753413495</v>
+        <v>0.1502326371243148</v>
       </c>
       <c r="C18">
-        <v>52.01976429014397</v>
+        <v>50.43953807398009</v>
       </c>
       <c r="D18">
-        <v>61.63596429014397</v>
+        <v>60.65743807398009</v>
       </c>
       <c r="E18">
-        <v>7.857200000000001</v>
+        <v>8.458900000000002</v>
       </c>
       <c r="F18">
-        <v>9.6272</v>
+        <v>10.2289</v>
       </c>
       <c r="G18">
         <v>0.011</v>
@@ -3144,45 +3144,45 @@
         <v>1.525</v>
       </c>
       <c r="M18">
-        <v>0.7297417600000001</v>
+        <v>0.9206010000000001</v>
       </c>
       <c r="N18">
-        <v>0.7952582399999998</v>
+        <v>0.6043989999999998</v>
       </c>
       <c r="O18">
-        <v>0.1988145599999999</v>
+        <v>0.1510997499999999</v>
       </c>
       <c r="P18">
-        <v>0.5964436799999998</v>
+        <v>0.4532992499999998</v>
       </c>
       <c r="Q18">
-        <v>1.43144368</v>
+        <v>1.28829925</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1660460420730352</v>
+        <v>0.1671778760533913</v>
       </c>
       <c r="T18">
-        <v>1.162871128779294</v>
+        <v>1.173816828410124</v>
       </c>
       <c r="U18">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.089780362850551</v>
+        <v>1.656526551676567</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3190,22 +3190,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1502326371243148</v>
+        <v>0.15018659890728</v>
       </c>
       <c r="C19">
-        <v>50.43953807398009</v>
+        <v>49.86459016982436</v>
       </c>
       <c r="D19">
-        <v>60.65743807398009</v>
+        <v>60.68419016982436</v>
       </c>
       <c r="E19">
-        <v>8.458900000000002</v>
+        <v>9.060600000000003</v>
       </c>
       <c r="F19">
-        <v>10.2289</v>
+        <v>10.8306</v>
       </c>
       <c r="G19">
         <v>0.011</v>
@@ -3226,28 +3226,28 @@
         <v>1.525</v>
       </c>
       <c r="M19">
-        <v>0.9206010000000001</v>
+        <v>0.9747540000000001</v>
       </c>
       <c r="N19">
-        <v>0.6043989999999998</v>
+        <v>0.5502459999999998</v>
       </c>
       <c r="O19">
-        <v>0.1510997499999999</v>
+        <v>0.1375614999999999</v>
       </c>
       <c r="P19">
-        <v>0.4532992499999998</v>
+        <v>0.4126844999999998</v>
       </c>
       <c r="Q19">
-        <v>1.28829925</v>
+        <v>1.2476845</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1671778760533913</v>
+        <v>0.1683373157405854</v>
       </c>
       <c r="T19">
-        <v>1.173816828410124</v>
+        <v>1.185029496324632</v>
       </c>
       <c r="U19">
         <v>0.09</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>1.656526551676567</v>
+        <v>1.564497298805647</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3272,22 +3272,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.15018659890728</v>
+        <v>0.1593277472792583</v>
       </c>
       <c r="C20">
-        <v>49.86459016982435</v>
+        <v>44.3766557516324</v>
       </c>
       <c r="D20">
-        <v>60.68419016982435</v>
+        <v>55.79795575163239</v>
       </c>
       <c r="E20">
-        <v>9.060600000000001</v>
+        <v>9.6623</v>
       </c>
       <c r="F20">
-        <v>10.8306</v>
+        <v>11.4323</v>
       </c>
       <c r="G20">
         <v>0.011</v>
@@ -3308,45 +3308,45 @@
         <v>1.525</v>
       </c>
       <c r="M20">
-        <v>0.974754</v>
+        <v>1.67826164</v>
       </c>
       <c r="N20">
-        <v>0.5502459999999999</v>
+        <v>-0.1532616400000002</v>
       </c>
       <c r="O20">
-        <v>0.1375615</v>
+        <v>-0.03831541000000005</v>
       </c>
       <c r="P20">
-        <v>0.4126844999999999</v>
+        <v>-0.1149462300000001</v>
       </c>
       <c r="Q20">
-        <v>1.2476845</v>
+        <v>0.7200537699999998</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1683373157405854</v>
+        <v>0.1700888411597792</v>
       </c>
       <c r="T20">
-        <v>1.185029496324632</v>
+        <v>1.201968085788279</v>
       </c>
       <c r="U20">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V20">
-        <v>0.25</v>
+        <v>0.2271695848330299</v>
       </c>
       <c r="W20">
-        <v>0.0675</v>
+        <v>0.1134515049465112</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y20">
-        <v>1.564497298805647</v>
+        <v>0.9086783393321197</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3354,22 +3354,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1593277472792583</v>
+        <v>0.1603377472792583</v>
       </c>
       <c r="C21">
-        <v>44.3766557516324</v>
+        <v>43.28292638447761</v>
       </c>
       <c r="D21">
-        <v>55.79795575163239</v>
+        <v>55.3059263844776</v>
       </c>
       <c r="E21">
-        <v>9.6623</v>
+        <v>10.264</v>
       </c>
       <c r="F21">
-        <v>11.4323</v>
+        <v>12.034</v>
       </c>
       <c r="G21">
         <v>0.011</v>
@@ -3390,37 +3390,37 @@
         <v>1.525</v>
       </c>
       <c r="M21">
-        <v>1.67826164</v>
+        <v>1.7665912</v>
       </c>
       <c r="N21">
-        <v>-0.1532616400000002</v>
+        <v>-0.2415912000000005</v>
       </c>
       <c r="O21">
-        <v>-0.03831541000000005</v>
+        <v>-0.06039780000000011</v>
       </c>
       <c r="P21">
-        <v>-0.1149462300000001</v>
+        <v>-0.1811934000000003</v>
       </c>
       <c r="Q21">
-        <v>0.7200537699999998</v>
+        <v>0.6538065999999996</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1700888411597792</v>
+        <v>0.1716424516742765</v>
       </c>
       <c r="T21">
-        <v>1.201968085788279</v>
+        <v>1.216992686860632</v>
       </c>
       <c r="U21">
         <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.2271695848330299</v>
+        <v>0.2158111055913784</v>
       </c>
       <c r="W21">
-        <v>0.1134515049465112</v>
+        <v>0.1151189296991857</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.9086783393321197</v>
+        <v>0.8632444223655137</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3436,22 +3436,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1603377472792583</v>
+        <v>0.1613477472792583</v>
       </c>
       <c r="C22">
-        <v>43.28292638447761</v>
+        <v>42.19779865037111</v>
       </c>
       <c r="D22">
-        <v>55.3059263844776</v>
+        <v>54.8224986503711</v>
       </c>
       <c r="E22">
-        <v>10.264</v>
+        <v>10.8657</v>
       </c>
       <c r="F22">
-        <v>12.034</v>
+        <v>12.6357</v>
       </c>
       <c r="G22">
         <v>0.011</v>
@@ -3472,37 +3472,37 @@
         <v>1.525</v>
       </c>
       <c r="M22">
-        <v>1.7665912</v>
+        <v>1.85492076</v>
       </c>
       <c r="N22">
-        <v>-0.2415912000000005</v>
+        <v>-0.3299207600000005</v>
       </c>
       <c r="O22">
-        <v>-0.06039780000000011</v>
+        <v>-0.08248019000000012</v>
       </c>
       <c r="P22">
-        <v>-0.1811934000000003</v>
+        <v>-0.2474405700000004</v>
       </c>
       <c r="Q22">
-        <v>0.6538065999999996</v>
+        <v>0.5875594299999995</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1716424516742765</v>
+        <v>0.1732353941005332</v>
       </c>
       <c r="T22">
-        <v>1.216992686860632</v>
+        <v>1.232397657580387</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.2158111055913784</v>
+        <v>0.2055343862775033</v>
       </c>
       <c r="W22">
-        <v>0.1151189296991857</v>
+        <v>0.1166275520944625</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.8632444223655137</v>
+        <v>0.822137545110013</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3518,22 +3518,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1613477472792583</v>
+        <v>0.1754590200662213</v>
       </c>
       <c r="C23">
-        <v>42.19779865037111</v>
+        <v>35.62956247785348</v>
       </c>
       <c r="D23">
-        <v>54.8224986503711</v>
+        <v>48.85596247785348</v>
       </c>
       <c r="E23">
-        <v>10.8657</v>
+        <v>11.4674</v>
       </c>
       <c r="F23">
-        <v>12.6357</v>
+        <v>13.2374</v>
       </c>
       <c r="G23">
         <v>0.011</v>
@@ -3554,45 +3554,45 @@
         <v>1.525</v>
       </c>
       <c r="M23">
-        <v>1.85492076</v>
+        <v>2.65806992</v>
       </c>
       <c r="N23">
-        <v>-0.3299207600000003</v>
+        <v>-1.133069920000001</v>
       </c>
       <c r="O23">
-        <v>-0.08248019000000006</v>
+        <v>-0.2832674800000001</v>
       </c>
       <c r="P23">
-        <v>-0.2474405700000002</v>
+        <v>-0.8498024400000004</v>
       </c>
       <c r="Q23">
-        <v>0.5875594299999998</v>
+        <v>-0.01480244000000042</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1732353941005332</v>
+        <v>0.1764349155466464</v>
       </c>
       <c r="T23">
-        <v>1.232397657580387</v>
+        <v>1.263339475302216</v>
       </c>
       <c r="U23">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.2055343862775033</v>
+        <v>0.1434311404419339</v>
       </c>
       <c r="W23">
-        <v>0.1166275520944625</v>
+        <v>0.1719990269992597</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y23">
-        <v>0.8221375451100131</v>
+        <v>0.5737245617677355</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3600,22 +3600,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1754590200662213</v>
+        <v>0.1770090200662213</v>
       </c>
       <c r="C24">
-        <v>35.62956247785348</v>
+        <v>34.45071662459999</v>
       </c>
       <c r="D24">
-        <v>48.85596247785348</v>
+        <v>48.27881662459999</v>
       </c>
       <c r="E24">
-        <v>11.4674</v>
+        <v>12.0691</v>
       </c>
       <c r="F24">
-        <v>13.2374</v>
+        <v>13.8391</v>
       </c>
       <c r="G24">
         <v>0.011</v>
@@ -3636,37 +3636,37 @@
         <v>1.525</v>
       </c>
       <c r="M24">
-        <v>2.65806992</v>
+        <v>2.77889128</v>
       </c>
       <c r="N24">
-        <v>-1.133069920000001</v>
+        <v>-1.25389128</v>
       </c>
       <c r="O24">
-        <v>-0.2832674800000001</v>
+        <v>-0.3134728200000001</v>
       </c>
       <c r="P24">
-        <v>-0.8498024400000004</v>
+        <v>-0.9404184600000003</v>
       </c>
       <c r="Q24">
-        <v>-0.01480244000000042</v>
+        <v>-0.1054184600000003</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1764349155466464</v>
+        <v>0.178131472891408</v>
       </c>
       <c r="T24">
-        <v>1.263339475302216</v>
+        <v>1.279746481474972</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1434311404419339</v>
+        <v>0.1371950039009802</v>
       </c>
       <c r="W24">
-        <v>0.1719990269992597</v>
+        <v>0.1732512432166832</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.5737245617677355</v>
+        <v>0.5487800156039209</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3682,22 +3682,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1770090200662213</v>
+        <v>0.1785590200662213</v>
       </c>
       <c r="C25">
-        <v>34.45071662459999</v>
+        <v>33.28534746124821</v>
       </c>
       <c r="D25">
-        <v>48.27881662459999</v>
+        <v>47.71514746124821</v>
       </c>
       <c r="E25">
-        <v>12.0691</v>
+        <v>12.6708</v>
       </c>
       <c r="F25">
-        <v>13.8391</v>
+        <v>14.4408</v>
       </c>
       <c r="G25">
         <v>0.011</v>
@@ -3718,37 +3718,37 @@
         <v>1.525</v>
       </c>
       <c r="M25">
-        <v>2.77889128</v>
+        <v>2.89971264</v>
       </c>
       <c r="N25">
-        <v>-1.25389128</v>
+        <v>-1.37471264</v>
       </c>
       <c r="O25">
-        <v>-0.3134728200000001</v>
+        <v>-0.3436781600000001</v>
       </c>
       <c r="P25">
-        <v>-0.9404184600000003</v>
+        <v>-1.03103448</v>
       </c>
       <c r="Q25">
-        <v>-0.1054184600000003</v>
+        <v>-0.1960344800000002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.178131472891408</v>
+        <v>0.1798726764820845</v>
       </c>
       <c r="T25">
-        <v>1.279746481474972</v>
+        <v>1.296585250968064</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1371950039009802</v>
+        <v>0.1314785454051061</v>
       </c>
       <c r="W25">
-        <v>0.1732512432166832</v>
+        <v>0.1743991080826547</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5487800156039209</v>
+        <v>0.5259141816204242</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3764,22 +3764,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1785590200662213</v>
+        <v>0.1801090200662213</v>
       </c>
       <c r="C26">
-        <v>33.28534746124821</v>
+        <v>32.13298840254561</v>
       </c>
       <c r="D26">
-        <v>47.71514746124821</v>
+        <v>47.1644884025456</v>
       </c>
       <c r="E26">
-        <v>12.6708</v>
+        <v>13.2725</v>
       </c>
       <c r="F26">
-        <v>14.4408</v>
+        <v>15.0425</v>
       </c>
       <c r="G26">
         <v>0.011</v>
@@ -3800,37 +3800,37 @@
         <v>1.525</v>
       </c>
       <c r="M26">
-        <v>2.89971264</v>
+        <v>3.020534</v>
       </c>
       <c r="N26">
-        <v>-1.37471264</v>
+        <v>-1.495534</v>
       </c>
       <c r="O26">
-        <v>-0.3436781600000001</v>
+        <v>-0.3738835</v>
       </c>
       <c r="P26">
-        <v>-1.03103448</v>
+        <v>-1.1216505</v>
       </c>
       <c r="Q26">
-        <v>-0.1960344800000002</v>
+        <v>-0.2866505000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1798726764820845</v>
+        <v>0.1816603121685123</v>
       </c>
       <c r="T26">
-        <v>1.296585250968064</v>
+        <v>1.313873054314305</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1314785454051061</v>
+        <v>0.1262194035889018</v>
       </c>
       <c r="W26">
-        <v>0.1743991080826547</v>
+        <v>0.1754551437593485</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5259141816204242</v>
+        <v>0.5048776143556073</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3846,22 +3846,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1801090200662213</v>
+        <v>0.1912518183871003</v>
       </c>
       <c r="C27">
-        <v>32.13298840254561</v>
+        <v>27.91810303295239</v>
       </c>
       <c r="D27">
-        <v>47.1644884025456</v>
+        <v>43.55130303295239</v>
       </c>
       <c r="E27">
-        <v>13.2725</v>
+        <v>13.8742</v>
       </c>
       <c r="F27">
-        <v>15.0425</v>
+        <v>15.6442</v>
       </c>
       <c r="G27">
         <v>0.011</v>
@@ -3882,45 +3882,45 @@
         <v>1.525</v>
       </c>
       <c r="M27">
-        <v>3.020534</v>
+        <v>3.688902360000001</v>
       </c>
       <c r="N27">
-        <v>-1.495534</v>
+        <v>-2.163902360000001</v>
       </c>
       <c r="O27">
-        <v>-0.3738835</v>
+        <v>-0.5409755900000002</v>
       </c>
       <c r="P27">
-        <v>-1.1216505</v>
+        <v>-1.622926770000001</v>
       </c>
       <c r="Q27">
-        <v>-0.2866505000000001</v>
+        <v>-0.7879267700000006</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1816603121685123</v>
+        <v>0.184162206009815</v>
       </c>
       <c r="T27">
-        <v>1.313873054314305</v>
+        <v>1.33806827991312</v>
       </c>
       <c r="U27">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.1262194035889018</v>
+        <v>0.1033505261982591</v>
       </c>
       <c r="W27">
-        <v>0.1754551437593485</v>
+        <v>0.2114299459224505</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y27">
-        <v>0.5048776143556073</v>
+        <v>0.4134021047930365</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3928,22 +3928,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1912518183871003</v>
+        <v>0.1931518183871003</v>
       </c>
       <c r="C28">
-        <v>27.91810303295239</v>
+        <v>26.75483903823311</v>
       </c>
       <c r="D28">
-        <v>43.55130303295239</v>
+        <v>42.98973903823311</v>
       </c>
       <c r="E28">
-        <v>13.8742</v>
+        <v>14.4759</v>
       </c>
       <c r="F28">
-        <v>15.6442</v>
+        <v>16.2459</v>
       </c>
       <c r="G28">
         <v>0.011</v>
@@ -3964,37 +3964,37 @@
         <v>1.525</v>
       </c>
       <c r="M28">
-        <v>3.688902360000001</v>
+        <v>3.830783220000001</v>
       </c>
       <c r="N28">
-        <v>-2.163902360000001</v>
+        <v>-2.305783220000001</v>
       </c>
       <c r="O28">
-        <v>-0.5409755900000002</v>
+        <v>-0.5764458050000002</v>
       </c>
       <c r="P28">
-        <v>-1.622926770000001</v>
+        <v>-1.729337415000001</v>
       </c>
       <c r="Q28">
-        <v>-0.7879267700000006</v>
+        <v>-0.8943374150000007</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.184162206009815</v>
+        <v>0.186057578694881</v>
       </c>
       <c r="T28">
-        <v>1.33806827991312</v>
+        <v>1.356397982377684</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1033505261982591</v>
+        <v>0.09952272893165694</v>
       </c>
       <c r="W28">
-        <v>0.2114299459224505</v>
+        <v>0.2123325405179153</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4134021047930365</v>
+        <v>0.3980909157266277</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4010,22 +4010,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1931518183871003</v>
+        <v>0.1950518183871003</v>
       </c>
       <c r="C29">
-        <v>26.75483903823311</v>
+        <v>25.60587264606899</v>
       </c>
       <c r="D29">
-        <v>42.98973903823311</v>
+        <v>42.44247264606899</v>
       </c>
       <c r="E29">
-        <v>14.4759</v>
+        <v>15.0776</v>
       </c>
       <c r="F29">
-        <v>16.2459</v>
+        <v>16.8476</v>
       </c>
       <c r="G29">
         <v>0.011</v>
@@ -4046,37 +4046,37 @@
         <v>1.525</v>
       </c>
       <c r="M29">
-        <v>3.830783220000001</v>
+        <v>3.972664080000001</v>
       </c>
       <c r="N29">
-        <v>-2.305783220000001</v>
+        <v>-2.447664080000001</v>
       </c>
       <c r="O29">
-        <v>-0.5764458050000002</v>
+        <v>-0.6119160200000002</v>
       </c>
       <c r="P29">
-        <v>-1.729337415000001</v>
+        <v>-1.835748060000001</v>
       </c>
       <c r="Q29">
-        <v>-0.8943374150000007</v>
+        <v>-1.000748060000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.186057578694881</v>
+        <v>0.1880056006211988</v>
       </c>
       <c r="T29">
-        <v>1.356397982377684</v>
+        <v>1.37523684324404</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.09952272893165694</v>
+        <v>0.09596834575552633</v>
       </c>
       <c r="W29">
-        <v>0.2123325405179153</v>
+        <v>0.2131706640708469</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3980909157266277</v>
+        <v>0.3838733830221053</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4092,22 +4092,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1950518183871003</v>
+        <v>0.1969518183871003</v>
       </c>
       <c r="C30">
-        <v>25.60587264606899</v>
+        <v>24.47066468772601</v>
       </c>
       <c r="D30">
-        <v>42.44247264606899</v>
+        <v>41.90896468772601</v>
       </c>
       <c r="E30">
-        <v>15.0776</v>
+        <v>15.6793</v>
       </c>
       <c r="F30">
-        <v>16.8476</v>
+        <v>17.4493</v>
       </c>
       <c r="G30">
         <v>0.011</v>
@@ -4128,37 +4128,37 @@
         <v>1.525</v>
       </c>
       <c r="M30">
-        <v>3.972664080000001</v>
+        <v>4.11454494</v>
       </c>
       <c r="N30">
-        <v>-2.447664080000001</v>
+        <v>-2.58954494</v>
       </c>
       <c r="O30">
-        <v>-0.6119160200000002</v>
+        <v>-0.647386235</v>
       </c>
       <c r="P30">
-        <v>-1.835748060000001</v>
+        <v>-1.942158705</v>
       </c>
       <c r="Q30">
-        <v>-1.000748060000001</v>
+        <v>-1.107158705</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1880056006211988</v>
+        <v>0.190008496404596</v>
       </c>
       <c r="T30">
-        <v>1.37523684324404</v>
+        <v>1.394606376247477</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.09596834575552633</v>
+        <v>0.09265909245361165</v>
       </c>
       <c r="W30">
-        <v>0.2131706640708469</v>
+        <v>0.2139509859994384</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3838733830221053</v>
+        <v>0.3706363698144466</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4174,22 +4174,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1969518183871002</v>
+        <v>0.1988518183871003</v>
       </c>
       <c r="C31">
-        <v>24.47066468772602</v>
+        <v>23.34870276764032</v>
       </c>
       <c r="D31">
-        <v>41.90896468772602</v>
+        <v>41.38870276764032</v>
       </c>
       <c r="E31">
-        <v>15.6793</v>
+        <v>16.281</v>
       </c>
       <c r="F31">
-        <v>17.4493</v>
+        <v>18.051</v>
       </c>
       <c r="G31">
         <v>0.011</v>
@@ -4210,37 +4210,37 @@
         <v>1.525</v>
       </c>
       <c r="M31">
-        <v>4.11454494</v>
+        <v>4.2564258</v>
       </c>
       <c r="N31">
-        <v>-2.58954494</v>
+        <v>-2.7314258</v>
       </c>
       <c r="O31">
-        <v>-0.647386235</v>
+        <v>-0.6828564499999999</v>
       </c>
       <c r="P31">
-        <v>-1.942158705</v>
+        <v>-2.04856935</v>
       </c>
       <c r="Q31">
-        <v>-1.107158705</v>
+        <v>-1.21356935</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.190008496404596</v>
+        <v>0.1920686177818045</v>
       </c>
       <c r="T31">
-        <v>1.394606376247477</v>
+        <v>1.414529324479584</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.09265909245361165</v>
+        <v>0.08957045603849126</v>
       </c>
       <c r="W31">
-        <v>0.2139509859994384</v>
+        <v>0.2146792864661238</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3706363698144466</v>
+        <v>0.358281824153965</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4256,22 +4256,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1988518183871003</v>
+        <v>0.2007518183871003</v>
       </c>
       <c r="C32">
-        <v>23.34870276764032</v>
+        <v>22.23949962197176</v>
       </c>
       <c r="D32">
-        <v>41.38870276764032</v>
+        <v>40.88119962197175</v>
       </c>
       <c r="E32">
-        <v>16.281</v>
+        <v>16.8827</v>
       </c>
       <c r="F32">
-        <v>18.051</v>
+        <v>18.6527</v>
       </c>
       <c r="G32">
         <v>0.011</v>
@@ -4292,37 +4292,37 @@
         <v>1.525</v>
       </c>
       <c r="M32">
-        <v>4.2564258</v>
+        <v>4.39830666</v>
       </c>
       <c r="N32">
-        <v>-2.7314258</v>
+        <v>-2.87330666</v>
       </c>
       <c r="O32">
-        <v>-0.6828564499999999</v>
+        <v>-0.7183266650000001</v>
       </c>
       <c r="P32">
-        <v>-2.04856935</v>
+        <v>-2.154979995</v>
       </c>
       <c r="Q32">
-        <v>-1.21356935</v>
+        <v>-1.319979995</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1920686177818045</v>
+        <v>0.1941884528221205</v>
       </c>
       <c r="T32">
-        <v>1.414529324479584</v>
+        <v>1.435029749472042</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.08957045603849126</v>
+        <v>0.0866810864888625</v>
       </c>
       <c r="W32">
-        <v>0.2146792864661238</v>
+        <v>0.2153605998059262</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.358281824153965</v>
+        <v>0.34672434595545</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4338,22 +4338,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2007518183871003</v>
+        <v>0.2026518183871002</v>
       </c>
       <c r="C33">
-        <v>22.23949962197176</v>
+        <v>21.14259159645783</v>
       </c>
       <c r="D33">
-        <v>40.88119962197175</v>
+        <v>40.38599159645783</v>
       </c>
       <c r="E33">
-        <v>16.8827</v>
+        <v>17.4844</v>
       </c>
       <c r="F33">
-        <v>18.6527</v>
+        <v>19.2544</v>
       </c>
       <c r="G33">
         <v>0.011</v>
@@ -4374,37 +4374,37 @@
         <v>1.525</v>
       </c>
       <c r="M33">
-        <v>4.39830666</v>
+        <v>4.54018752</v>
       </c>
       <c r="N33">
-        <v>-2.87330666</v>
+        <v>-3.01518752</v>
       </c>
       <c r="O33">
-        <v>-0.7183266650000001</v>
+        <v>-0.75379688</v>
       </c>
       <c r="P33">
-        <v>-2.154979995</v>
+        <v>-2.26139064</v>
       </c>
       <c r="Q33">
-        <v>-1.319979995</v>
+        <v>-1.42639064</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1941884528221205</v>
+        <v>0.1963706359518576</v>
       </c>
       <c r="T33">
-        <v>1.435029749472042</v>
+        <v>1.456133128140749</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.0866810864888625</v>
+        <v>0.08397230253608555</v>
       </c>
       <c r="W33">
-        <v>0.2153605998059262</v>
+        <v>0.215999331061991</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.34672434595545</v>
+        <v>0.3358892101443423</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4420,22 +4420,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2026518183871002</v>
+        <v>0.2045518183871003</v>
       </c>
       <c r="C34">
-        <v>21.14259159645783</v>
+        <v>20.05753723357321</v>
       </c>
       <c r="D34">
-        <v>40.38599159645783</v>
+        <v>39.90263723357321</v>
       </c>
       <c r="E34">
-        <v>17.4844</v>
+        <v>18.0861</v>
       </c>
       <c r="F34">
-        <v>19.2544</v>
+        <v>19.8561</v>
       </c>
       <c r="G34">
         <v>0.011</v>
@@ -4456,37 +4456,37 @@
         <v>1.525</v>
       </c>
       <c r="M34">
-        <v>4.54018752</v>
+        <v>4.68206838</v>
       </c>
       <c r="N34">
-        <v>-3.01518752</v>
+        <v>-3.157068380000001</v>
       </c>
       <c r="O34">
-        <v>-0.75379688</v>
+        <v>-0.7892670950000001</v>
       </c>
       <c r="P34">
-        <v>-2.26139064</v>
+        <v>-2.367801285000001</v>
       </c>
       <c r="Q34">
-        <v>-1.42639064</v>
+        <v>-1.532801285000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1963706359518576</v>
+        <v>0.1986179588765122</v>
       </c>
       <c r="T34">
-        <v>1.456133128140749</v>
+        <v>1.477866458411506</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.08397230253608555</v>
+        <v>0.08142768730771932</v>
       </c>
       <c r="W34">
-        <v>0.215999331061991</v>
+        <v>0.2165993513328398</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3358892101443423</v>
+        <v>0.3257107492308773</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4502,22 +4502,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2045518183871003</v>
+        <v>0.2064518183871003</v>
       </c>
       <c r="C35">
-        <v>20.05753723357321</v>
+        <v>18.98391595994586</v>
       </c>
       <c r="D35">
-        <v>39.90263723357321</v>
+        <v>39.43071595994586</v>
       </c>
       <c r="E35">
-        <v>18.0861</v>
+        <v>18.6878</v>
       </c>
       <c r="F35">
-        <v>19.8561</v>
+        <v>20.4578</v>
       </c>
       <c r="G35">
         <v>0.011</v>
@@ -4538,37 +4538,37 @@
         <v>1.525</v>
       </c>
       <c r="M35">
-        <v>4.68206838</v>
+        <v>4.823949240000001</v>
       </c>
       <c r="N35">
-        <v>-3.157068380000001</v>
+        <v>-3.298949240000001</v>
       </c>
       <c r="O35">
-        <v>-0.7892670950000001</v>
+        <v>-0.8247373100000003</v>
       </c>
       <c r="P35">
-        <v>-2.367801285000001</v>
+        <v>-2.474211930000001</v>
       </c>
       <c r="Q35">
-        <v>-1.532801285000001</v>
+        <v>-1.639211930000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1986179588765122</v>
+        <v>0.2009333824958533</v>
       </c>
       <c r="T35">
-        <v>1.477866458411506</v>
+        <v>1.500258374448044</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.08142768730771932</v>
+        <v>0.0790327553280805</v>
       </c>
       <c r="W35">
-        <v>0.2165993513328398</v>
+        <v>0.2171640762936386</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3257107492308773</v>
+        <v>0.3161310213123221</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4584,22 +4584,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2064518183871003</v>
+        <v>0.2083518183871002</v>
       </c>
       <c r="C36">
-        <v>18.98391595994586</v>
+        <v>17.92132686582645</v>
       </c>
       <c r="D36">
-        <v>39.43071595994586</v>
+        <v>38.96982686582645</v>
       </c>
       <c r="E36">
-        <v>18.6878</v>
+        <v>19.2895</v>
       </c>
       <c r="F36">
-        <v>20.4578</v>
+        <v>21.0595</v>
       </c>
       <c r="G36">
         <v>0.011</v>
@@ -4620,37 +4620,37 @@
         <v>1.525</v>
       </c>
       <c r="M36">
-        <v>4.823949240000001</v>
+        <v>4.965830100000001</v>
       </c>
       <c r="N36">
-        <v>-3.298949240000001</v>
+        <v>-3.440830100000001</v>
       </c>
       <c r="O36">
-        <v>-0.8247373100000003</v>
+        <v>-0.8602075250000002</v>
       </c>
       <c r="P36">
-        <v>-2.474211930000001</v>
+        <v>-2.580622575</v>
       </c>
       <c r="Q36">
-        <v>-1.639211930000001</v>
+        <v>-1.745622575000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2009333824958533</v>
+        <v>0.2033200499188663</v>
       </c>
       <c r="T36">
-        <v>1.500258374448044</v>
+        <v>1.523339272516475</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0790327553280805</v>
+        <v>0.07677467660442107</v>
       </c>
       <c r="W36">
-        <v>0.2171640762936386</v>
+        <v>0.2176965312566775</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3161310213123221</v>
+        <v>0.3070987064176842</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4666,22 +4666,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2083518183871002</v>
+        <v>0.2102518183871002</v>
       </c>
       <c r="C37">
-        <v>17.92132686582645</v>
+        <v>16.86938756916642</v>
       </c>
       <c r="D37">
-        <v>38.96982686582645</v>
+        <v>38.51958756916642</v>
       </c>
       <c r="E37">
-        <v>19.2895</v>
+        <v>19.8912</v>
       </c>
       <c r="F37">
-        <v>21.0595</v>
+        <v>21.6612</v>
       </c>
       <c r="G37">
         <v>0.011</v>
@@ -4702,37 +4702,37 @@
         <v>1.525</v>
       </c>
       <c r="M37">
-        <v>4.965830100000001</v>
+        <v>5.107710960000001</v>
       </c>
       <c r="N37">
-        <v>-3.440830100000001</v>
+        <v>-3.582710960000001</v>
       </c>
       <c r="O37">
-        <v>-0.8602075250000002</v>
+        <v>-0.8956777400000003</v>
       </c>
       <c r="P37">
-        <v>-2.580622575</v>
+        <v>-2.687033220000001</v>
       </c>
       <c r="Q37">
-        <v>-1.745622575000001</v>
+        <v>-1.852033220000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2033200499188663</v>
+        <v>0.2057813006988486</v>
       </c>
       <c r="T37">
-        <v>1.523339272516475</v>
+        <v>1.547141448649545</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.07677467660442107</v>
+        <v>0.07464204669874269</v>
       </c>
       <c r="W37">
-        <v>0.2176965312566775</v>
+        <v>0.2181994053884365</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3070987064176842</v>
+        <v>0.2985681867949708</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4748,22 +4748,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2102518183871002</v>
+        <v>0.2121518183871003</v>
       </c>
       <c r="C38">
-        <v>16.86938756916642</v>
+        <v>15.82773315754039</v>
       </c>
       <c r="D38">
-        <v>38.51958756916642</v>
+        <v>38.07963315754039</v>
       </c>
       <c r="E38">
-        <v>19.8912</v>
+        <v>20.4929</v>
       </c>
       <c r="F38">
-        <v>21.6612</v>
+        <v>22.2629</v>
       </c>
       <c r="G38">
         <v>0.011</v>
@@ -4784,37 +4784,37 @@
         <v>1.525</v>
       </c>
       <c r="M38">
-        <v>5.10771096</v>
+        <v>5.249591820000001</v>
       </c>
       <c r="N38">
-        <v>-3.58271096</v>
+        <v>-3.724591820000001</v>
       </c>
       <c r="O38">
-        <v>-0.8956777400000001</v>
+        <v>-0.9311479550000002</v>
       </c>
       <c r="P38">
-        <v>-2.68703322</v>
+        <v>-2.793443865000001</v>
       </c>
       <c r="Q38">
-        <v>-1.85203322</v>
+        <v>-1.958443865000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2057813006988486</v>
+        <v>0.2083206864242272</v>
       </c>
       <c r="T38">
-        <v>1.547141448649545</v>
+        <v>1.57169924942176</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07464204669874271</v>
+        <v>0.07262469408526318</v>
       </c>
       <c r="W38">
-        <v>0.2181994053884365</v>
+        <v>0.218675097134695</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2985681867949709</v>
+        <v>0.2904987763410527</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4830,22 +4830,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2121518183871003</v>
+        <v>0.2140518183871003</v>
       </c>
       <c r="C39">
-        <v>15.82773315754039</v>
+        <v>14.79601520175897</v>
       </c>
       <c r="D39">
-        <v>38.07963315754039</v>
+        <v>37.64961520175897</v>
       </c>
       <c r="E39">
-        <v>20.4929</v>
+        <v>21.0946</v>
       </c>
       <c r="F39">
-        <v>22.2629</v>
+        <v>22.8646</v>
       </c>
       <c r="G39">
         <v>0.011</v>
@@ -4866,37 +4866,37 @@
         <v>1.525</v>
       </c>
       <c r="M39">
-        <v>5.249591820000001</v>
+        <v>5.39147268</v>
       </c>
       <c r="N39">
-        <v>-3.724591820000001</v>
+        <v>-3.86647268</v>
       </c>
       <c r="O39">
-        <v>-0.9311479550000002</v>
+        <v>-0.9666181699999999</v>
       </c>
       <c r="P39">
-        <v>-2.793443865000001</v>
+        <v>-2.89985451</v>
       </c>
       <c r="Q39">
-        <v>-1.958443865000001</v>
+        <v>-2.06485451</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2083206864242272</v>
+        <v>0.2109419878181663</v>
       </c>
       <c r="T39">
-        <v>1.57169924942176</v>
+        <v>1.59704923731566</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.07262469408526318</v>
+        <v>0.07071351792512467</v>
       </c>
       <c r="W39">
-        <v>0.218675097134695</v>
+        <v>0.2191257524732556</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2904987763410527</v>
+        <v>0.2828540717004987</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4912,22 +4912,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2140518183871003</v>
+        <v>0.2159518183871003</v>
       </c>
       <c r="C40">
-        <v>14.79601520175897</v>
+        <v>13.77390083556865</v>
       </c>
       <c r="D40">
-        <v>37.64961520175897</v>
+        <v>37.22920083556865</v>
       </c>
       <c r="E40">
-        <v>21.0946</v>
+        <v>21.6963</v>
       </c>
       <c r="F40">
-        <v>22.8646</v>
+        <v>23.4663</v>
       </c>
       <c r="G40">
         <v>0.011</v>
@@ -4948,37 +4948,37 @@
         <v>1.525</v>
       </c>
       <c r="M40">
-        <v>5.39147268</v>
+        <v>5.53335354</v>
       </c>
       <c r="N40">
-        <v>-3.86647268</v>
+        <v>-4.00835354</v>
       </c>
       <c r="O40">
-        <v>-0.9666181699999999</v>
+        <v>-1.002088385</v>
       </c>
       <c r="P40">
-        <v>-2.89985451</v>
+        <v>-3.006265155</v>
       </c>
       <c r="Q40">
-        <v>-2.06485451</v>
+        <v>-2.171265155</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2109419878181663</v>
+        <v>0.2136492335201035</v>
       </c>
       <c r="T40">
-        <v>1.59704923731566</v>
+        <v>1.623230372353621</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.07071351792512467</v>
+        <v>0.06890035079883942</v>
       </c>
       <c r="W40">
-        <v>0.2191257524732556</v>
+        <v>0.2195532972816337</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2828540717004987</v>
+        <v>0.2756014031953578</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4994,22 +4994,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2159518183871003</v>
+        <v>0.2178518183871003</v>
       </c>
       <c r="C41">
-        <v>13.77390083556865</v>
+        <v>12.76107189632995</v>
       </c>
       <c r="D41">
-        <v>37.22920083556865</v>
+        <v>36.81807189632995</v>
       </c>
       <c r="E41">
-        <v>21.6963</v>
+        <v>22.298</v>
       </c>
       <c r="F41">
-        <v>23.4663</v>
+        <v>24.068</v>
       </c>
       <c r="G41">
         <v>0.011</v>
@@ -5030,37 +5030,37 @@
         <v>1.525</v>
       </c>
       <c r="M41">
-        <v>5.53335354</v>
+        <v>5.675234400000001</v>
       </c>
       <c r="N41">
-        <v>-4.00835354</v>
+        <v>-4.1502344</v>
       </c>
       <c r="O41">
-        <v>-1.002088385</v>
+        <v>-1.0375586</v>
       </c>
       <c r="P41">
-        <v>-3.006265155</v>
+        <v>-3.1126758</v>
       </c>
       <c r="Q41">
-        <v>-2.171265155</v>
+        <v>-2.2776758</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2136492335201035</v>
+        <v>0.2164467207454386</v>
       </c>
       <c r="T41">
-        <v>1.623230372353621</v>
+        <v>1.650284211892848</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06890035079883942</v>
+        <v>0.06717784202886844</v>
       </c>
       <c r="W41">
-        <v>0.2195532972816337</v>
+        <v>0.2199594648495928</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2756014031953578</v>
+        <v>0.2687113681154738</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5076,22 +5076,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2178518183871003</v>
+        <v>0.2197518183871003</v>
       </c>
       <c r="C42">
-        <v>12.76107189632995</v>
+        <v>11.75722412201145</v>
       </c>
       <c r="D42">
-        <v>36.81807189632995</v>
+        <v>36.41592412201145</v>
       </c>
       <c r="E42">
-        <v>22.298</v>
+        <v>22.8997</v>
       </c>
       <c r="F42">
-        <v>24.068</v>
+        <v>24.6697</v>
       </c>
       <c r="G42">
         <v>0.011</v>
@@ -5112,37 +5112,37 @@
         <v>1.525</v>
       </c>
       <c r="M42">
-        <v>5.675234400000001</v>
+        <v>5.81711526</v>
       </c>
       <c r="N42">
-        <v>-4.1502344</v>
+        <v>-4.292115260000001</v>
       </c>
       <c r="O42">
-        <v>-1.0375586</v>
+        <v>-1.073028815</v>
       </c>
       <c r="P42">
-        <v>-3.1126758</v>
+        <v>-3.219086445000001</v>
       </c>
       <c r="Q42">
-        <v>-2.2776758</v>
+        <v>-2.384086445000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2164467207454386</v>
+        <v>0.2193390380462087</v>
       </c>
       <c r="T42">
-        <v>1.650284211892848</v>
+        <v>1.67825513073849</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06717784202886844</v>
+        <v>0.06553935807694482</v>
       </c>
       <c r="W42">
-        <v>0.2199594648495928</v>
+        <v>0.2203458193654564</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2687113681154738</v>
+        <v>0.2621574323077792</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5158,22 +5158,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2197518183871003</v>
+        <v>0.2216518183871002</v>
       </c>
       <c r="C43">
-        <v>11.75722412201145</v>
+        <v>10.76206640024077</v>
       </c>
       <c r="D43">
-        <v>36.41592412201145</v>
+        <v>36.02246640024077</v>
       </c>
       <c r="E43">
-        <v>22.8997</v>
+        <v>23.5014</v>
       </c>
       <c r="F43">
-        <v>24.6697</v>
+        <v>25.2714</v>
       </c>
       <c r="G43">
         <v>0.011</v>
@@ -5194,37 +5194,37 @@
         <v>1.525</v>
       </c>
       <c r="M43">
-        <v>5.81711526</v>
+        <v>5.958996120000001</v>
       </c>
       <c r="N43">
-        <v>-4.292115260000001</v>
+        <v>-4.433996120000002</v>
       </c>
       <c r="O43">
-        <v>-1.073028815</v>
+        <v>-1.10849903</v>
       </c>
       <c r="P43">
-        <v>-3.219086445000001</v>
+        <v>-3.325497090000001</v>
       </c>
       <c r="Q43">
-        <v>-2.384086445000001</v>
+        <v>-2.490497090000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2193390380462087</v>
+        <v>0.2223310904263157</v>
       </c>
       <c r="T43">
-        <v>1.67825513073849</v>
+        <v>1.707190564027085</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06553935807694482</v>
+        <v>0.06397889717035089</v>
       </c>
       <c r="W43">
-        <v>0.2203458193654564</v>
+        <v>0.2207137760472313</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2621574323077792</v>
+        <v>0.2559155886814035</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5240,22 +5240,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2216518183871003</v>
+        <v>0.2235518183871003</v>
       </c>
       <c r="C44">
-        <v>10.76206640024076</v>
+        <v>9.775320065516887</v>
       </c>
       <c r="D44">
-        <v>36.02246640024076</v>
+        <v>35.63742006551688</v>
       </c>
       <c r="E44">
-        <v>23.5014</v>
+        <v>24.1031</v>
       </c>
       <c r="F44">
-        <v>25.2714</v>
+        <v>25.8731</v>
       </c>
       <c r="G44">
         <v>0.011</v>
@@ -5276,37 +5276,37 @@
         <v>1.525</v>
       </c>
       <c r="M44">
-        <v>5.95899612</v>
+        <v>6.100876980000001</v>
       </c>
       <c r="N44">
-        <v>-4.43399612</v>
+        <v>-4.57587698</v>
       </c>
       <c r="O44">
-        <v>-1.10849903</v>
+        <v>-1.143969245</v>
       </c>
       <c r="P44">
-        <v>-3.32549709</v>
+        <v>-3.431907735</v>
       </c>
       <c r="Q44">
-        <v>-2.49049709</v>
+        <v>-2.596907735</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2223310904263157</v>
+        <v>0.2254281271004616</v>
       </c>
       <c r="T44">
-        <v>1.707190564027084</v>
+        <v>1.737141275676682</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06397889717035089</v>
+        <v>0.06249101584080784</v>
       </c>
       <c r="W44">
-        <v>0.2207137760472313</v>
+        <v>0.2210646184647375</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2559155886814036</v>
+        <v>0.2499640633632315</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5322,22 +5322,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2235518183871003</v>
+        <v>0.2254518183871003</v>
       </c>
       <c r="C45">
-        <v>9.775320065516887</v>
+        <v>8.79671824101888</v>
       </c>
       <c r="D45">
-        <v>35.63742006551688</v>
+        <v>35.26051824101888</v>
       </c>
       <c r="E45">
-        <v>24.1031</v>
+        <v>24.7048</v>
       </c>
       <c r="F45">
-        <v>25.8731</v>
+        <v>26.4748</v>
       </c>
       <c r="G45">
         <v>0.011</v>
@@ -5358,37 +5358,37 @@
         <v>1.525</v>
       </c>
       <c r="M45">
-        <v>6.100876980000001</v>
+        <v>6.24275784</v>
       </c>
       <c r="N45">
-        <v>-4.57587698</v>
+        <v>-4.717757840000001</v>
       </c>
       <c r="O45">
-        <v>-1.143969245</v>
+        <v>-1.17943946</v>
       </c>
       <c r="P45">
-        <v>-3.431907735</v>
+        <v>-3.538318380000001</v>
       </c>
       <c r="Q45">
-        <v>-2.596907735</v>
+        <v>-2.703318380000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2254281271004616</v>
+        <v>0.2286357722272556</v>
       </c>
       <c r="T45">
-        <v>1.737141275676682</v>
+        <v>1.76816165559948</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06249101584080784</v>
+        <v>0.06107076548078949</v>
       </c>
       <c r="W45">
-        <v>0.2210646184647375</v>
+        <v>0.2213995134996299</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2499640633632315</v>
+        <v>0.2442830619231579</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5404,22 +5404,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2254518183871003</v>
+        <v>0.2273518183871003</v>
       </c>
       <c r="C46">
-        <v>8.79671824101888</v>
+        <v>7.826005221743628</v>
       </c>
       <c r="D46">
-        <v>35.26051824101888</v>
+        <v>34.89150522174363</v>
       </c>
       <c r="E46">
-        <v>24.7048</v>
+        <v>25.3065</v>
       </c>
       <c r="F46">
-        <v>26.4748</v>
+        <v>27.0765</v>
       </c>
       <c r="G46">
         <v>0.011</v>
@@ -5440,37 +5440,37 @@
         <v>1.525</v>
       </c>
       <c r="M46">
-        <v>6.24275784</v>
+        <v>6.384638700000001</v>
       </c>
       <c r="N46">
-        <v>-4.717757840000001</v>
+        <v>-4.859638700000001</v>
       </c>
       <c r="O46">
-        <v>-1.17943946</v>
+        <v>-1.214909675</v>
       </c>
       <c r="P46">
-        <v>-3.538318380000001</v>
+        <v>-3.644729025000001</v>
       </c>
       <c r="Q46">
-        <v>-2.703318380000001</v>
+        <v>-2.809729025000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2286357722272556</v>
+        <v>0.2319600589950239</v>
       </c>
       <c r="T46">
-        <v>1.76816165559948</v>
+        <v>1.800310049337653</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06107076548078949</v>
+        <v>0.05971363735899416</v>
       </c>
       <c r="W46">
-        <v>0.2213995134996299</v>
+        <v>0.2217195243107492</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2442830619231579</v>
+        <v>0.2388545494359766</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5486,22 +5486,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2273518183871003</v>
+        <v>0.2292518183871003</v>
       </c>
       <c r="C47">
-        <v>7.826005221743628</v>
+        <v>6.862935895976431</v>
       </c>
       <c r="D47">
-        <v>34.89150522174363</v>
+        <v>34.53013589597643</v>
       </c>
       <c r="E47">
-        <v>25.3065</v>
+        <v>25.9082</v>
       </c>
       <c r="F47">
-        <v>27.0765</v>
+        <v>27.6782</v>
       </c>
       <c r="G47">
         <v>0.011</v>
@@ -5522,37 +5522,37 @@
         <v>1.525</v>
       </c>
       <c r="M47">
-        <v>6.384638700000001</v>
+        <v>6.526519560000001</v>
       </c>
       <c r="N47">
-        <v>-4.859638700000001</v>
+        <v>-5.00151956</v>
       </c>
       <c r="O47">
-        <v>-1.214909675</v>
+        <v>-1.25037989</v>
       </c>
       <c r="P47">
-        <v>-3.644729025000001</v>
+        <v>-3.75113967</v>
       </c>
       <c r="Q47">
-        <v>-2.809729025000001</v>
+        <v>-2.91613967</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2319600589950239</v>
+        <v>0.2354074674949317</v>
       </c>
       <c r="T47">
-        <v>1.800310049337653</v>
+        <v>1.833649124325387</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05971363735899416</v>
+        <v>0.05841551480771168</v>
       </c>
       <c r="W47">
-        <v>0.2217195243107492</v>
+        <v>0.2220256216083416</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2388545494359766</v>
+        <v>0.2336620592308468</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5568,22 +5568,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2292518183871003</v>
+        <v>0.2311518183871002</v>
       </c>
       <c r="C48">
-        <v>6.862935895976431</v>
+        <v>5.907275202343872</v>
       </c>
       <c r="D48">
-        <v>34.53013589597643</v>
+        <v>34.17617520234387</v>
       </c>
       <c r="E48">
-        <v>25.9082</v>
+        <v>26.5099</v>
       </c>
       <c r="F48">
-        <v>27.6782</v>
+        <v>28.2799</v>
       </c>
       <c r="G48">
         <v>0.011</v>
@@ -5604,37 +5604,37 @@
         <v>1.525</v>
       </c>
       <c r="M48">
-        <v>6.526519560000001</v>
+        <v>6.66840042</v>
       </c>
       <c r="N48">
-        <v>-5.00151956</v>
+        <v>-5.143400420000001</v>
       </c>
       <c r="O48">
-        <v>-1.25037989</v>
+        <v>-1.285850105</v>
       </c>
       <c r="P48">
-        <v>-3.75113967</v>
+        <v>-3.857550315000001</v>
       </c>
       <c r="Q48">
-        <v>-2.91613967</v>
+        <v>-3.022550315000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2354074674949317</v>
+        <v>0.2389849668816285</v>
       </c>
       <c r="T48">
-        <v>1.833649124325387</v>
+        <v>1.868246277614545</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05841551480771168</v>
+        <v>0.05717263151393059</v>
       </c>
       <c r="W48">
-        <v>0.2220256216083416</v>
+        <v>0.2223186934890152</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2336620592308468</v>
+        <v>0.2286905260557223</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5650,22 +5650,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2311518183871002</v>
+        <v>0.2330518183871003</v>
       </c>
       <c r="C49">
-        <v>5.907275202343872</v>
+        <v>4.958797619921594</v>
       </c>
       <c r="D49">
-        <v>34.17617520234387</v>
+        <v>33.82939761992159</v>
       </c>
       <c r="E49">
-        <v>26.5099</v>
+        <v>27.1116</v>
       </c>
       <c r="F49">
-        <v>28.2799</v>
+        <v>28.8816</v>
       </c>
       <c r="G49">
         <v>0.011</v>
@@ -5686,37 +5686,37 @@
         <v>1.525</v>
       </c>
       <c r="M49">
-        <v>6.66840042</v>
+        <v>6.810281280000001</v>
       </c>
       <c r="N49">
-        <v>-5.143400420000001</v>
+        <v>-5.285281280000001</v>
       </c>
       <c r="O49">
-        <v>-1.285850105</v>
+        <v>-1.32132032</v>
       </c>
       <c r="P49">
-        <v>-3.857550315000001</v>
+        <v>-3.963960960000001</v>
       </c>
       <c r="Q49">
-        <v>-3.022550315000001</v>
+        <v>-3.128960960000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2389849668816285</v>
+        <v>0.242700062398583</v>
       </c>
       <c r="T49">
-        <v>1.868246277614545</v>
+        <v>1.904174090645594</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05717263151393059</v>
+        <v>0.05598153502405703</v>
       </c>
       <c r="W49">
-        <v>0.2223186934890152</v>
+        <v>0.2225995540413274</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2286905260557223</v>
+        <v>0.223926140096228</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5732,22 +5732,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2330518183871003</v>
+        <v>0.2349518183871002</v>
       </c>
       <c r="C50">
-        <v>4.958797619921597</v>
+        <v>4.017286689072861</v>
       </c>
       <c r="D50">
-        <v>33.82939761992159</v>
+        <v>33.48958668907286</v>
       </c>
       <c r="E50">
-        <v>27.1116</v>
+        <v>27.7133</v>
       </c>
       <c r="F50">
-        <v>28.8816</v>
+        <v>29.4833</v>
       </c>
       <c r="G50">
         <v>0.011</v>
@@ -5768,37 +5768,37 @@
         <v>1.525</v>
       </c>
       <c r="M50">
-        <v>6.81028128</v>
+        <v>6.95216214</v>
       </c>
       <c r="N50">
-        <v>-5.28528128</v>
+        <v>-5.42716214</v>
       </c>
       <c r="O50">
-        <v>-1.32132032</v>
+        <v>-1.356790535</v>
       </c>
       <c r="P50">
-        <v>-3.96396096</v>
+        <v>-4.070371605</v>
       </c>
       <c r="Q50">
-        <v>-3.12896096</v>
+        <v>-3.235371605</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2427000623985829</v>
+        <v>0.24656084793581</v>
       </c>
       <c r="T50">
-        <v>1.904174090645594</v>
+        <v>1.941510837520998</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05598153502405703</v>
+        <v>0.05483905471744362</v>
       </c>
       <c r="W50">
-        <v>0.2225995540413274</v>
+        <v>0.2228689508976268</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2239261400962282</v>
+        <v>0.2193562188697745</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5814,22 +5814,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2349518183871002</v>
+        <v>0.2368518183871002</v>
       </c>
       <c r="C51">
-        <v>4.017286689072861</v>
+        <v>3.082534560878436</v>
       </c>
       <c r="D51">
-        <v>33.48958668907286</v>
+        <v>33.15653456087843</v>
       </c>
       <c r="E51">
-        <v>27.7133</v>
+        <v>28.315</v>
       </c>
       <c r="F51">
-        <v>29.4833</v>
+        <v>30.085</v>
       </c>
       <c r="G51">
         <v>0.011</v>
@@ -5850,37 +5850,37 @@
         <v>1.525</v>
       </c>
       <c r="M51">
-        <v>6.95216214</v>
+        <v>7.094043</v>
       </c>
       <c r="N51">
-        <v>-5.42716214</v>
+        <v>-5.569043000000001</v>
       </c>
       <c r="O51">
-        <v>-1.356790535</v>
+        <v>-1.39226075</v>
       </c>
       <c r="P51">
-        <v>-4.070371605</v>
+        <v>-4.17678225</v>
       </c>
       <c r="Q51">
-        <v>-3.235371605</v>
+        <v>-3.341782250000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.24656084793581</v>
+        <v>0.2505760648945262</v>
       </c>
       <c r="T51">
-        <v>1.941510837520998</v>
+        <v>1.980341054271418</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05483905471744362</v>
+        <v>0.05374227362309476</v>
       </c>
       <c r="W51">
-        <v>0.2228689508976268</v>
+        <v>0.2231275718796742</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2193562188697745</v>
+        <v>0.214969094492379</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5896,22 +5896,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2368518183871002</v>
+        <v>0.2387518183871002</v>
       </c>
       <c r="C52">
-        <v>3.082534560878436</v>
+        <v>2.15434157318716</v>
       </c>
       <c r="D52">
-        <v>33.15653456087843</v>
+        <v>32.83004157318716</v>
       </c>
       <c r="E52">
-        <v>28.315</v>
+        <v>28.9167</v>
       </c>
       <c r="F52">
-        <v>30.085</v>
+        <v>30.6867</v>
       </c>
       <c r="G52">
         <v>0.011</v>
@@ -5932,37 +5932,37 @@
         <v>1.525</v>
       </c>
       <c r="M52">
-        <v>7.094043</v>
+        <v>7.235923860000001</v>
       </c>
       <c r="N52">
-        <v>-5.569043000000001</v>
+        <v>-5.710923860000001</v>
       </c>
       <c r="O52">
-        <v>-1.39226075</v>
+        <v>-1.427730965</v>
       </c>
       <c r="P52">
-        <v>-4.17678225</v>
+        <v>-4.283192895000001</v>
       </c>
       <c r="Q52">
-        <v>-3.341782250000001</v>
+        <v>-3.448192895000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2505760648945262</v>
+        <v>0.2547551682597207</v>
       </c>
       <c r="T52">
-        <v>1.980341054271418</v>
+        <v>2.020756177827978</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05374227362309476</v>
+        <v>0.05268850355205368</v>
       </c>
       <c r="W52">
-        <v>0.2231275718796742</v>
+        <v>0.2233760508624258</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.214969094492379</v>
+        <v>0.2107540142082146</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5978,22 +5978,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2387518183871002</v>
+        <v>0.2406518183871003</v>
       </c>
       <c r="C53">
-        <v>2.15434157318716</v>
+        <v>1.232515851470076</v>
       </c>
       <c r="D53">
-        <v>32.83004157318716</v>
+        <v>32.50991585147008</v>
       </c>
       <c r="E53">
-        <v>28.9167</v>
+        <v>29.5184</v>
       </c>
       <c r="F53">
-        <v>30.6867</v>
+        <v>31.2884</v>
       </c>
       <c r="G53">
         <v>0.011</v>
@@ -6014,37 +6014,37 @@
         <v>1.525</v>
       </c>
       <c r="M53">
-        <v>7.235923860000001</v>
+        <v>7.377804720000001</v>
       </c>
       <c r="N53">
-        <v>-5.710923860000001</v>
+        <v>-5.852804720000002</v>
       </c>
       <c r="O53">
-        <v>-1.427730965</v>
+        <v>-1.46320118</v>
       </c>
       <c r="P53">
-        <v>-4.283192895000001</v>
+        <v>-4.389603540000001</v>
       </c>
       <c r="Q53">
-        <v>-3.448192895000001</v>
+        <v>-3.554603540000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2547551682597207</v>
+        <v>0.2591084009317982</v>
       </c>
       <c r="T53">
-        <v>2.020756177827978</v>
+        <v>2.062855264866061</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05268850355205368</v>
+        <v>0.05167526309912956</v>
       </c>
       <c r="W53">
-        <v>0.2233760508624258</v>
+        <v>0.2236149729612253</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2107540142082146</v>
+        <v>0.2067010523965181</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6060,22 +6060,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2406518183871003</v>
+        <v>0.2425518183871003</v>
       </c>
       <c r="C54">
-        <v>1.232515851470076</v>
+        <v>0.3168729328015161</v>
       </c>
       <c r="D54">
-        <v>32.50991585147008</v>
+        <v>32.19597293280152</v>
       </c>
       <c r="E54">
-        <v>29.5184</v>
+        <v>30.1201</v>
       </c>
       <c r="F54">
-        <v>31.2884</v>
+        <v>31.8901</v>
       </c>
       <c r="G54">
         <v>0.011</v>
@@ -6096,37 +6096,37 @@
         <v>1.525</v>
       </c>
       <c r="M54">
-        <v>7.377804720000001</v>
+        <v>7.519685580000001</v>
       </c>
       <c r="N54">
-        <v>-5.852804720000002</v>
+        <v>-5.994685580000001</v>
       </c>
       <c r="O54">
-        <v>-1.46320118</v>
+        <v>-1.498671395</v>
       </c>
       <c r="P54">
-        <v>-4.389603540000001</v>
+        <v>-4.496014185</v>
       </c>
       <c r="Q54">
-        <v>-3.554603540000001</v>
+        <v>-3.661014185</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2591084009317982</v>
+        <v>0.2636468775473684</v>
       </c>
       <c r="T54">
-        <v>2.062855264866061</v>
+        <v>2.106745802416402</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05167526309912956</v>
+        <v>0.05070025813499505</v>
       </c>
       <c r="W54">
-        <v>0.2236149729612253</v>
+        <v>0.2238448791317682</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2067010523965181</v>
+        <v>0.2028010325399803</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6142,22 +6142,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2425518183871003</v>
+        <v>0.2444518183871003</v>
       </c>
       <c r="C55">
-        <v>0.3168729328015161</v>
+        <v>-0.5927645885813497</v>
       </c>
       <c r="D55">
-        <v>32.19597293280152</v>
+        <v>31.88803541141866</v>
       </c>
       <c r="E55">
-        <v>30.1201</v>
+        <v>30.72180000000001</v>
       </c>
       <c r="F55">
-        <v>31.8901</v>
+        <v>32.4918</v>
       </c>
       <c r="G55">
         <v>0.011</v>
@@ -6178,37 +6178,37 @@
         <v>1.525</v>
       </c>
       <c r="M55">
-        <v>7.519685580000001</v>
+        <v>7.661566440000001</v>
       </c>
       <c r="N55">
-        <v>-5.994685580000001</v>
+        <v>-6.136566440000001</v>
       </c>
       <c r="O55">
-        <v>-1.498671395</v>
+        <v>-1.53414161</v>
       </c>
       <c r="P55">
-        <v>-4.496014185</v>
+        <v>-4.60242483</v>
       </c>
       <c r="Q55">
-        <v>-3.661014185</v>
+        <v>-3.76742483</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2636468775473684</v>
+        <v>0.2683826792331807</v>
       </c>
       <c r="T55">
-        <v>2.106745802416402</v>
+        <v>2.152544624208063</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05070025813499505</v>
+        <v>0.04976136446582847</v>
       </c>
       <c r="W55">
-        <v>0.2238448791317682</v>
+        <v>0.2240662702589576</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2028010325399803</v>
+        <v>0.199045457863314</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6224,22 +6224,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2444518183871003</v>
+        <v>0.2463518183871003</v>
       </c>
       <c r="C56">
-        <v>-0.5927645885813497</v>
+        <v>-1.496567395571372</v>
       </c>
       <c r="D56">
-        <v>31.88803541141866</v>
+        <v>31.58593260442863</v>
       </c>
       <c r="E56">
-        <v>30.72180000000001</v>
+        <v>31.32350000000001</v>
       </c>
       <c r="F56">
-        <v>32.4918</v>
+        <v>33.09350000000001</v>
       </c>
       <c r="G56">
         <v>0.011</v>
@@ -6260,37 +6260,37 @@
         <v>1.525</v>
       </c>
       <c r="M56">
-        <v>7.661566440000001</v>
+        <v>7.803447300000002</v>
       </c>
       <c r="N56">
-        <v>-6.136566440000001</v>
+        <v>-6.278447300000002</v>
       </c>
       <c r="O56">
-        <v>-1.53414161</v>
+        <v>-1.569611825</v>
       </c>
       <c r="P56">
-        <v>-4.60242483</v>
+        <v>-4.708835475000001</v>
       </c>
       <c r="Q56">
-        <v>-3.76742483</v>
+        <v>-3.873835475000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2683826792331807</v>
+        <v>0.2733289609939181</v>
       </c>
       <c r="T56">
-        <v>2.152544624208063</v>
+        <v>2.200378949190465</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04976136446582847</v>
+        <v>0.04885661238463158</v>
       </c>
       <c r="W56">
-        <v>0.2240662702589576</v>
+        <v>0.2242796107997039</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.199045457863314</v>
+        <v>0.1954264495385264</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6306,22 +6306,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2463518183871003</v>
+        <v>0.2482518183871003</v>
       </c>
       <c r="C57">
-        <v>-1.496567395571372</v>
+        <v>-2.394699763660388</v>
       </c>
       <c r="D57">
-        <v>31.58593260442863</v>
+        <v>31.28950023633962</v>
       </c>
       <c r="E57">
-        <v>31.32350000000001</v>
+        <v>31.92520000000001</v>
       </c>
       <c r="F57">
-        <v>33.09350000000001</v>
+        <v>33.69520000000001</v>
       </c>
       <c r="G57">
         <v>0.011</v>
@@ -6342,37 +6342,37 @@
         <v>1.525</v>
       </c>
       <c r="M57">
-        <v>7.803447300000002</v>
+        <v>7.945328160000002</v>
       </c>
       <c r="N57">
-        <v>-6.278447300000002</v>
+        <v>-6.420328160000002</v>
       </c>
       <c r="O57">
-        <v>-1.569611825</v>
+        <v>-1.605082040000001</v>
       </c>
       <c r="P57">
-        <v>-4.708835475000001</v>
+        <v>-4.815246120000001</v>
       </c>
       <c r="Q57">
-        <v>-3.873835475000001</v>
+        <v>-3.980246120000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2733289609939181</v>
+        <v>0.2785000737437798</v>
       </c>
       <c r="T57">
-        <v>2.200378949190465</v>
+        <v>2.250387561672066</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04885661238463158</v>
+        <v>0.04798417287776317</v>
       </c>
       <c r="W57">
-        <v>0.2242796107997039</v>
+        <v>0.2244853320354235</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1954264495385264</v>
+        <v>0.1919366915110526</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6388,22 +6388,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2482518183871003</v>
+        <v>0.2501518183871003</v>
       </c>
       <c r="C58">
-        <v>-2.394699763660388</v>
+        <v>-3.287319858809379</v>
       </c>
       <c r="D58">
-        <v>31.28950023633962</v>
+        <v>30.99858014119063</v>
       </c>
       <c r="E58">
-        <v>31.92520000000001</v>
+        <v>32.5269</v>
       </c>
       <c r="F58">
-        <v>33.69520000000001</v>
+        <v>34.29690000000001</v>
       </c>
       <c r="G58">
         <v>0.011</v>
@@ -6424,37 +6424,37 @@
         <v>1.525</v>
       </c>
       <c r="M58">
-        <v>7.945328160000002</v>
+        <v>8.087209020000003</v>
       </c>
       <c r="N58">
-        <v>-6.420328160000002</v>
+        <v>-6.562209020000003</v>
       </c>
       <c r="O58">
-        <v>-1.605082040000001</v>
+        <v>-1.640552255000001</v>
       </c>
       <c r="P58">
-        <v>-4.815246120000001</v>
+        <v>-4.921656765000002</v>
       </c>
       <c r="Q58">
-        <v>-3.980246120000001</v>
+        <v>-4.086656765000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2785000737437798</v>
+        <v>0.2839117033657282</v>
       </c>
       <c r="T58">
-        <v>2.250387561672066</v>
+        <v>2.302722156129556</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04798417287776317</v>
+        <v>0.04714234528341643</v>
       </c>
       <c r="W58">
-        <v>0.2244853320354235</v>
+        <v>0.2246838349821704</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1919366915110526</v>
+        <v>0.1885693811336658</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6470,22 +6470,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2501518183871003</v>
+        <v>0.2520518183871003</v>
       </c>
       <c r="C59">
-        <v>-3.287319858809379</v>
+        <v>-4.174580018854719</v>
       </c>
       <c r="D59">
-        <v>30.99858014119063</v>
+        <v>30.71301998114528</v>
       </c>
       <c r="E59">
-        <v>32.5269</v>
+        <v>33.1286</v>
       </c>
       <c r="F59">
-        <v>34.29690000000001</v>
+        <v>34.8986</v>
       </c>
       <c r="G59">
         <v>0.011</v>
@@ -6506,37 +6506,37 @@
         <v>1.525</v>
       </c>
       <c r="M59">
-        <v>8.087209020000003</v>
+        <v>8.22908988</v>
       </c>
       <c r="N59">
-        <v>-6.562209020000003</v>
+        <v>-6.70408988</v>
       </c>
       <c r="O59">
-        <v>-1.640552255000001</v>
+        <v>-1.67602247</v>
       </c>
       <c r="P59">
-        <v>-4.921656765000002</v>
+        <v>-5.02806741</v>
       </c>
       <c r="Q59">
-        <v>-4.086656765000002</v>
+        <v>-4.19306741</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2839117033657282</v>
+        <v>0.2895810296363408</v>
       </c>
       <c r="T59">
-        <v>2.302722156129556</v>
+        <v>2.357548874132641</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04714234528341643</v>
+        <v>0.04632954622680582</v>
       </c>
       <c r="W59">
-        <v>0.2246838349821704</v>
+        <v>0.2248754929997192</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1885693811336658</v>
+        <v>0.1853181849072233</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6552,22 +6552,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2520518183871002</v>
+        <v>0.2539518183871002</v>
       </c>
       <c r="C60">
-        <v>-4.174580018854705</v>
+        <v>-5.056627019502347</v>
       </c>
       <c r="D60">
-        <v>30.7130199811453</v>
+        <v>30.43267298049765</v>
       </c>
       <c r="E60">
-        <v>33.1286</v>
+        <v>33.73029999999999</v>
       </c>
       <c r="F60">
-        <v>34.8986</v>
+        <v>35.5003</v>
       </c>
       <c r="G60">
         <v>0.011</v>
@@ -6588,37 +6588,37 @@
         <v>1.525</v>
       </c>
       <c r="M60">
-        <v>8.22908988</v>
+        <v>8.370970739999999</v>
       </c>
       <c r="N60">
-        <v>-6.70408988</v>
+        <v>-6.845970739999999</v>
       </c>
       <c r="O60">
-        <v>-1.67602247</v>
+        <v>-1.711492685</v>
       </c>
       <c r="P60">
-        <v>-5.02806741</v>
+        <v>-5.134478054999999</v>
       </c>
       <c r="Q60">
-        <v>-4.19306741</v>
+        <v>-4.299478054999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2895810296363407</v>
+        <v>0.2955269084079589</v>
       </c>
       <c r="T60">
-        <v>2.35754887413264</v>
+        <v>2.415050066184656</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04632954622680582</v>
+        <v>0.04554429968058878</v>
       </c>
       <c r="W60">
-        <v>0.2248754929997192</v>
+        <v>0.2250606541353172</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1853181849072233</v>
+        <v>0.1821771987223552</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6634,22 +6634,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2539518183871002</v>
+        <v>0.2558518183871002</v>
       </c>
       <c r="C61">
-        <v>-5.056627019502347</v>
+        <v>-5.933602325885968</v>
       </c>
       <c r="D61">
-        <v>30.43267298049765</v>
+        <v>30.15739767411403</v>
       </c>
       <c r="E61">
-        <v>33.73029999999999</v>
+        <v>34.33199999999999</v>
       </c>
       <c r="F61">
-        <v>35.5003</v>
+        <v>36.102</v>
       </c>
       <c r="G61">
         <v>0.011</v>
@@ -6670,37 +6670,37 @@
         <v>1.525</v>
       </c>
       <c r="M61">
-        <v>8.370970739999999</v>
+        <v>8.512851599999999</v>
       </c>
       <c r="N61">
-        <v>-6.845970739999999</v>
+        <v>-6.987851599999999</v>
       </c>
       <c r="O61">
-        <v>-1.711492685</v>
+        <v>-1.7469629</v>
       </c>
       <c r="P61">
-        <v>-5.134478054999999</v>
+        <v>-5.240888699999999</v>
       </c>
       <c r="Q61">
-        <v>-4.299478054999999</v>
+        <v>-4.405888699999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2955269084079589</v>
+        <v>0.3017700811181578</v>
       </c>
       <c r="T61">
-        <v>2.415050066184656</v>
+        <v>2.475426317839272</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04554429968058878</v>
+        <v>0.04478522801924563</v>
       </c>
       <c r="W61">
-        <v>0.2250606541353172</v>
+        <v>0.2252396432330619</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1821771987223552</v>
+        <v>0.1791409120769826</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6716,22 +6716,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2558518183871002</v>
+        <v>0.2577518183871003</v>
       </c>
       <c r="C62">
-        <v>-5.933602325885968</v>
+        <v>-6.805642330594814</v>
       </c>
       <c r="D62">
-        <v>30.15739767411403</v>
+        <v>29.88705766940518</v>
       </c>
       <c r="E62">
-        <v>34.33199999999999</v>
+        <v>34.93369999999999</v>
       </c>
       <c r="F62">
-        <v>36.102</v>
+        <v>36.7037</v>
       </c>
       <c r="G62">
         <v>0.011</v>
@@ -6752,37 +6752,37 @@
         <v>1.525</v>
       </c>
       <c r="M62">
-        <v>8.512851599999999</v>
+        <v>8.65473246</v>
       </c>
       <c r="N62">
-        <v>-6.987851599999999</v>
+        <v>-7.12973246</v>
       </c>
       <c r="O62">
-        <v>-1.7469629</v>
+        <v>-1.782433115</v>
       </c>
       <c r="P62">
-        <v>-5.240888699999999</v>
+        <v>-5.347299345</v>
       </c>
       <c r="Q62">
-        <v>-4.405888699999999</v>
+        <v>-4.512299345</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3017700811181578</v>
+        <v>0.308333416531444</v>
       </c>
       <c r="T62">
-        <v>2.475426317839272</v>
+        <v>2.538898787527459</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04478522801924563</v>
+        <v>0.04405104395335636</v>
       </c>
       <c r="W62">
-        <v>0.2252396432330619</v>
+        <v>0.2254127638357986</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1791409120769826</v>
+        <v>0.1762041758134255</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6798,22 +6798,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2577518183871003</v>
+        <v>0.2596518183871003</v>
       </c>
       <c r="C63">
-        <v>-6.805642330594814</v>
+        <v>-7.672878579012782</v>
       </c>
       <c r="D63">
-        <v>29.88705766940518</v>
+        <v>29.62152142098722</v>
       </c>
       <c r="E63">
-        <v>34.93369999999999</v>
+        <v>35.5354</v>
       </c>
       <c r="F63">
-        <v>36.7037</v>
+        <v>37.3054</v>
       </c>
       <c r="G63">
         <v>0.011</v>
@@ -6834,37 +6834,37 @@
         <v>1.525</v>
       </c>
       <c r="M63">
-        <v>8.65473246</v>
+        <v>8.796613320000001</v>
       </c>
       <c r="N63">
-        <v>-7.12973246</v>
+        <v>-7.27161332</v>
       </c>
       <c r="O63">
-        <v>-1.782433115</v>
+        <v>-1.81790333</v>
       </c>
       <c r="P63">
-        <v>-5.347299345</v>
+        <v>-5.45370999</v>
       </c>
       <c r="Q63">
-        <v>-4.512299345</v>
+        <v>-4.61870999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.308333416531444</v>
+        <v>0.3152421906506925</v>
       </c>
       <c r="T63">
-        <v>2.538898787527459</v>
+        <v>2.605711913515024</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04405104395335636</v>
+        <v>0.04334054324443125</v>
       </c>
       <c r="W63">
-        <v>0.2254127638357986</v>
+        <v>0.2255802999029631</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1762041758134255</v>
+        <v>0.173362172977725</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6880,22 +6880,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2596518183871003</v>
+        <v>0.2615518183871003</v>
       </c>
       <c r="C64">
-        <v>-7.672878579012782</v>
+        <v>-8.535437982750906</v>
       </c>
       <c r="D64">
-        <v>29.62152142098722</v>
+        <v>29.36066201724909</v>
       </c>
       <c r="E64">
-        <v>35.5354</v>
+        <v>36.1371</v>
       </c>
       <c r="F64">
-        <v>37.3054</v>
+        <v>37.9071</v>
       </c>
       <c r="G64">
         <v>0.011</v>
@@ -6916,37 +6916,37 @@
         <v>1.525</v>
       </c>
       <c r="M64">
-        <v>8.796613320000001</v>
+        <v>8.938494180000001</v>
       </c>
       <c r="N64">
-        <v>-7.27161332</v>
+        <v>-7.413494180000001</v>
       </c>
       <c r="O64">
-        <v>-1.81790333</v>
+        <v>-1.853373545</v>
       </c>
       <c r="P64">
-        <v>-5.45370999</v>
+        <v>-5.560120635000001</v>
       </c>
       <c r="Q64">
-        <v>-4.61870999</v>
+        <v>-4.725120635000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3152421906506925</v>
+        <v>0.3225244120196301</v>
       </c>
       <c r="T64">
-        <v>2.605711913515024</v>
+        <v>2.676136559826241</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04334054324443125</v>
+        <v>0.04265259811356726</v>
       </c>
       <c r="W64">
-        <v>0.2255802999029631</v>
+        <v>0.2257425173648208</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.173362172977725</v>
+        <v>0.1706103924542691</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6962,22 +6962,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2615518183871003</v>
+        <v>0.2634518183871002</v>
       </c>
       <c r="C65">
-        <v>-8.535437982750906</v>
+        <v>-9.3934430219009</v>
       </c>
       <c r="D65">
-        <v>29.36066201724909</v>
+        <v>29.1043569780991</v>
       </c>
       <c r="E65">
-        <v>36.1371</v>
+        <v>36.7388</v>
       </c>
       <c r="F65">
-        <v>37.9071</v>
+        <v>38.5088</v>
       </c>
       <c r="G65">
         <v>0.011</v>
@@ -6998,37 +6998,37 @@
         <v>1.525</v>
       </c>
       <c r="M65">
-        <v>8.938494180000001</v>
+        <v>9.08037504</v>
       </c>
       <c r="N65">
-        <v>-7.413494180000001</v>
+        <v>-7.555375039999999</v>
       </c>
       <c r="O65">
-        <v>-1.853373545</v>
+        <v>-1.88884376</v>
       </c>
       <c r="P65">
-        <v>-5.560120635000001</v>
+        <v>-5.666531279999999</v>
       </c>
       <c r="Q65">
-        <v>-4.725120635000001</v>
+        <v>-4.831531279999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3225244120196301</v>
+        <v>0.3302112012423976</v>
       </c>
       <c r="T65">
-        <v>2.676136559826241</v>
+        <v>2.750473686488081</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04265259811356726</v>
+        <v>0.04198615126804277</v>
       </c>
       <c r="W65">
-        <v>0.2257425173648208</v>
+        <v>0.2258996655309955</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1706103924542691</v>
+        <v>0.1679446050721711</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7044,22 +7044,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2634518183871002</v>
+        <v>0.2653518183871003</v>
       </c>
       <c r="C66">
-        <v>-9.3934430219009</v>
+        <v>-10.24701193678682</v>
       </c>
       <c r="D66">
-        <v>29.1043569780991</v>
+        <v>28.85248806321318</v>
       </c>
       <c r="E66">
-        <v>36.7388</v>
+        <v>37.3405</v>
       </c>
       <c r="F66">
-        <v>38.5088</v>
+        <v>39.1105</v>
       </c>
       <c r="G66">
         <v>0.011</v>
@@ -7080,37 +7080,37 @@
         <v>1.525</v>
       </c>
       <c r="M66">
-        <v>9.08037504</v>
+        <v>9.2222559</v>
       </c>
       <c r="N66">
-        <v>-7.555375039999999</v>
+        <v>-7.6972559</v>
       </c>
       <c r="O66">
-        <v>-1.88884376</v>
+        <v>-1.924313975</v>
       </c>
       <c r="P66">
-        <v>-5.666531279999999</v>
+        <v>-5.772941925</v>
       </c>
       <c r="Q66">
-        <v>-4.831531279999999</v>
+        <v>-4.937941925</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3302112012423976</v>
+        <v>0.338337235563609</v>
       </c>
       <c r="T66">
-        <v>2.750473686488081</v>
+        <v>2.829058648959169</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04198615126804277</v>
+        <v>0.04134021047930365</v>
       </c>
       <c r="W66">
-        <v>0.2258996655309955</v>
+        <v>0.2260519783689802</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1679446050721711</v>
+        <v>0.1653608419172147</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7126,22 +7126,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2653518183871003</v>
+        <v>0.2672518183871003</v>
       </c>
       <c r="C67">
-        <v>-10.24701193678682</v>
+        <v>-11.09625890984567</v>
       </c>
       <c r="D67">
-        <v>28.85248806321318</v>
+        <v>28.60494109015433</v>
       </c>
       <c r="E67">
-        <v>37.3405</v>
+        <v>37.9422</v>
       </c>
       <c r="F67">
-        <v>39.1105</v>
+        <v>39.7122</v>
       </c>
       <c r="G67">
         <v>0.011</v>
@@ -7162,37 +7162,37 @@
         <v>1.525</v>
       </c>
       <c r="M67">
-        <v>9.2222559</v>
+        <v>9.364136760000001</v>
       </c>
       <c r="N67">
-        <v>-7.6972559</v>
+        <v>-7.839136760000001</v>
       </c>
       <c r="O67">
-        <v>-1.924313975</v>
+        <v>-1.95978419</v>
       </c>
       <c r="P67">
-        <v>-5.772941925</v>
+        <v>-5.87935257</v>
       </c>
       <c r="Q67">
-        <v>-4.937941925</v>
+        <v>-5.04435257</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.338337235563609</v>
+        <v>0.3469412719037151</v>
       </c>
       <c r="T67">
-        <v>2.829058648959169</v>
+        <v>2.912266256281497</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04134021047930365</v>
+        <v>0.04071384365385966</v>
       </c>
       <c r="W67">
-        <v>0.2260519783689802</v>
+        <v>0.2261996756664199</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1653608419172147</v>
+        <v>0.1628553746154386</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7208,22 +7208,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2672518183871003</v>
+        <v>0.2691518183871003</v>
       </c>
       <c r="C68">
-        <v>-11.09625890984567</v>
+        <v>-11.94129423822477</v>
       </c>
       <c r="D68">
-        <v>28.60494109015433</v>
+        <v>28.36160576177524</v>
       </c>
       <c r="E68">
-        <v>37.9422</v>
+        <v>38.5439</v>
       </c>
       <c r="F68">
-        <v>39.7122</v>
+        <v>40.3139</v>
       </c>
       <c r="G68">
         <v>0.011</v>
@@ -7244,37 +7244,37 @@
         <v>1.525</v>
       </c>
       <c r="M68">
-        <v>9.364136760000001</v>
+        <v>9.506017620000002</v>
       </c>
       <c r="N68">
-        <v>-7.839136760000001</v>
+        <v>-7.981017620000001</v>
       </c>
       <c r="O68">
-        <v>-1.95978419</v>
+        <v>-1.995254405</v>
       </c>
       <c r="P68">
-        <v>-5.87935257</v>
+        <v>-5.985763215</v>
       </c>
       <c r="Q68">
-        <v>-5.04435257</v>
+        <v>-5.150763215</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3469412719037151</v>
+        <v>0.3560667649917065</v>
       </c>
       <c r="T68">
-        <v>2.912266256281497</v>
+        <v>3.000516748896088</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04071384365385966</v>
+        <v>0.04010617434559309</v>
       </c>
       <c r="W68">
-        <v>0.2261996756664199</v>
+        <v>0.2263429640893092</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1628553746154386</v>
+        <v>0.1604246973823724</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7290,22 +7290,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2691518183871003</v>
+        <v>0.2710518183871002</v>
       </c>
       <c r="C69">
-        <v>-11.94129423822477</v>
+        <v>-12.78222449764388</v>
       </c>
       <c r="D69">
-        <v>28.36160576177524</v>
+        <v>28.12237550235612</v>
       </c>
       <c r="E69">
-        <v>38.5439</v>
+        <v>39.1456</v>
       </c>
       <c r="F69">
-        <v>40.3139</v>
+        <v>40.9156</v>
       </c>
       <c r="G69">
         <v>0.011</v>
@@ -7326,37 +7326,37 @@
         <v>1.525</v>
       </c>
       <c r="M69">
-        <v>9.506017620000002</v>
+        <v>9.647898480000002</v>
       </c>
       <c r="N69">
-        <v>-7.981017620000001</v>
+        <v>-8.122898480000002</v>
       </c>
       <c r="O69">
-        <v>-1.995254405</v>
+        <v>-2.03072462</v>
       </c>
       <c r="P69">
-        <v>-5.985763215</v>
+        <v>-6.092173860000001</v>
       </c>
       <c r="Q69">
-        <v>-5.150763215</v>
+        <v>-5.257173860000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3560667649917065</v>
+        <v>0.3657626013976973</v>
       </c>
       <c r="T69">
-        <v>3.000516748896088</v>
+        <v>3.094282897299091</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04010617434559309</v>
+        <v>0.03951637766404025</v>
       </c>
       <c r="W69">
-        <v>0.2263429640893092</v>
+        <v>0.2264820381468193</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1604246973823724</v>
+        <v>0.158065510656161</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7372,22 +7372,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2710518183871002</v>
+        <v>0.2729518183871003</v>
       </c>
       <c r="C70">
-        <v>-12.78222449764388</v>
+        <v>-13.61915269803372</v>
       </c>
       <c r="D70">
-        <v>28.12237550235612</v>
+        <v>27.88714730196628</v>
       </c>
       <c r="E70">
-        <v>39.1456</v>
+        <v>39.7473</v>
       </c>
       <c r="F70">
-        <v>40.9156</v>
+        <v>41.51730000000001</v>
       </c>
       <c r="G70">
         <v>0.011</v>
@@ -7408,37 +7408,37 @@
         <v>1.525</v>
       </c>
       <c r="M70">
-        <v>9.647898480000002</v>
+        <v>9.789779340000003</v>
       </c>
       <c r="N70">
-        <v>-8.122898480000002</v>
+        <v>-8.264779340000002</v>
       </c>
       <c r="O70">
-        <v>-2.03072462</v>
+        <v>-2.066194835000001</v>
       </c>
       <c r="P70">
-        <v>-6.092173860000001</v>
+        <v>-6.198584505000001</v>
       </c>
       <c r="Q70">
-        <v>-5.257173860000001</v>
+        <v>-5.363584505000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3657626013976973</v>
+        <v>0.3760839756363328</v>
       </c>
       <c r="T70">
-        <v>3.094282897299091</v>
+        <v>3.19409847463132</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03951637766404025</v>
+        <v>0.03894367653847445</v>
       </c>
       <c r="W70">
-        <v>0.2264820381468193</v>
+        <v>0.2266170810722277</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.158065510656161</v>
+        <v>0.1557747061538979</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7454,22 +7454,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2729518183871003</v>
+        <v>0.2748518183871003</v>
       </c>
       <c r="C71">
-        <v>-13.61915269803372</v>
+        <v>-14.4521784314282</v>
       </c>
       <c r="D71">
-        <v>27.88714730196628</v>
+        <v>27.65582156857181</v>
       </c>
       <c r="E71">
-        <v>39.7473</v>
+        <v>40.349</v>
       </c>
       <c r="F71">
-        <v>41.51730000000001</v>
+        <v>42.11900000000001</v>
       </c>
       <c r="G71">
         <v>0.011</v>
@@ -7490,37 +7490,37 @@
         <v>1.525</v>
       </c>
       <c r="M71">
-        <v>9.789779340000003</v>
+        <v>9.931660200000001</v>
       </c>
       <c r="N71">
-        <v>-8.264779340000002</v>
+        <v>-8.406660200000001</v>
       </c>
       <c r="O71">
-        <v>-2.066194835000001</v>
+        <v>-2.10166505</v>
       </c>
       <c r="P71">
-        <v>-6.198584505000001</v>
+        <v>-6.304995150000001</v>
       </c>
       <c r="Q71">
-        <v>-5.363584505000001</v>
+        <v>-5.469995150000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3760839756363328</v>
+        <v>0.3870934414908772</v>
       </c>
       <c r="T71">
-        <v>3.19409847463132</v>
+        <v>3.300568423785697</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03894367653847445</v>
+        <v>0.03838733830221053</v>
       </c>
       <c r="W71">
-        <v>0.2266170810722277</v>
+        <v>0.2267482656283388</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1557747061538979</v>
+        <v>0.1535493532088422</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7536,22 +7536,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2748518183871003</v>
+        <v>0.2767518183871003</v>
       </c>
       <c r="C72">
-        <v>-14.4521784314282</v>
+        <v>-15.28139801255665</v>
       </c>
       <c r="D72">
-        <v>27.65582156857181</v>
+        <v>27.42830198744336</v>
       </c>
       <c r="E72">
-        <v>40.349</v>
+        <v>40.9507</v>
       </c>
       <c r="F72">
-        <v>42.11900000000001</v>
+        <v>42.72070000000001</v>
       </c>
       <c r="G72">
         <v>0.011</v>
@@ -7572,37 +7572,37 @@
         <v>1.525</v>
       </c>
       <c r="M72">
-        <v>9.931660200000001</v>
+        <v>10.07354106</v>
       </c>
       <c r="N72">
-        <v>-8.406660200000001</v>
+        <v>-8.548541060000002</v>
       </c>
       <c r="O72">
-        <v>-2.10166505</v>
+        <v>-2.137135265</v>
       </c>
       <c r="P72">
-        <v>-6.304995150000001</v>
+        <v>-6.411405795000001</v>
       </c>
       <c r="Q72">
-        <v>-5.469995150000001</v>
+        <v>-5.576405795000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3870934414908772</v>
+        <v>0.3988621808526316</v>
       </c>
       <c r="T72">
-        <v>3.300568423785697</v>
+        <v>3.41438112805417</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03838733830221053</v>
+        <v>0.03784667156555968</v>
       </c>
       <c r="W72">
-        <v>0.2267482656283388</v>
+        <v>0.226875754844841</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1535493532088422</v>
+        <v>0.1513866862622387</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7618,22 +7618,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2767518183871003</v>
+        <v>0.2786518183871002</v>
       </c>
       <c r="C73">
-        <v>-15.28139801255664</v>
+        <v>-16.10690461255281</v>
       </c>
       <c r="D73">
-        <v>27.42830198744336</v>
+        <v>27.20449538744719</v>
       </c>
       <c r="E73">
-        <v>40.9507</v>
+        <v>41.5524</v>
       </c>
       <c r="F73">
-        <v>42.7207</v>
+        <v>43.3224</v>
       </c>
       <c r="G73">
         <v>0.011</v>
@@ -7654,37 +7654,37 @@
         <v>1.525</v>
       </c>
       <c r="M73">
-        <v>10.07354106</v>
+        <v>10.21542192</v>
       </c>
       <c r="N73">
-        <v>-8.54854106</v>
+        <v>-8.69042192</v>
       </c>
       <c r="O73">
-        <v>-2.137135265</v>
+        <v>-2.17260548</v>
       </c>
       <c r="P73">
-        <v>-6.411405795</v>
+        <v>-6.517816440000001</v>
       </c>
       <c r="Q73">
-        <v>-5.576405795</v>
+        <v>-5.682816440000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3988621808526315</v>
+        <v>0.4114715444545111</v>
       </c>
       <c r="T73">
-        <v>3.414381128054169</v>
+        <v>3.53632331119896</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03784667156555969</v>
+        <v>0.03732102334937135</v>
       </c>
       <c r="W73">
-        <v>0.226875754844841</v>
+        <v>0.2269997026942182</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1513866862622388</v>
+        <v>0.1492840933974855</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7700,22 +7700,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2786518183871002</v>
+        <v>0.2805518183871002</v>
       </c>
       <c r="C74">
-        <v>-16.10690461255281</v>
+        <v>-16.92878838617077</v>
       </c>
       <c r="D74">
-        <v>27.20449538744719</v>
+        <v>26.98431161382923</v>
       </c>
       <c r="E74">
-        <v>41.5524</v>
+        <v>42.1541</v>
       </c>
       <c r="F74">
-        <v>43.3224</v>
+        <v>43.9241</v>
       </c>
       <c r="G74">
         <v>0.011</v>
@@ -7736,37 +7736,37 @@
         <v>1.525</v>
       </c>
       <c r="M74">
-        <v>10.21542192</v>
+        <v>10.35730278</v>
       </c>
       <c r="N74">
-        <v>-8.69042192</v>
+        <v>-8.832302780000001</v>
       </c>
       <c r="O74">
-        <v>-2.17260548</v>
+        <v>-2.208075695</v>
       </c>
       <c r="P74">
-        <v>-6.517816440000001</v>
+        <v>-6.624227085000001</v>
       </c>
       <c r="Q74">
-        <v>-5.682816440000001</v>
+        <v>-5.789227085000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4114715444545111</v>
+        <v>0.4250149349898634</v>
       </c>
       <c r="T74">
-        <v>3.53632331119896</v>
+        <v>3.667298248650773</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03732102334937135</v>
+        <v>0.03680977645417449</v>
       </c>
       <c r="W74">
-        <v>0.2269997026942182</v>
+        <v>0.2271202547121057</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1492840933974855</v>
+        <v>0.147239105816698</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7782,22 +7782,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2805518183871002</v>
+        <v>0.2824518183871003</v>
       </c>
       <c r="C75">
-        <v>-16.92878838617077</v>
+        <v>-17.74713659287253</v>
       </c>
       <c r="D75">
-        <v>26.98431161382923</v>
+        <v>26.76766340712747</v>
       </c>
       <c r="E75">
-        <v>42.1541</v>
+        <v>42.7558</v>
       </c>
       <c r="F75">
-        <v>43.9241</v>
+        <v>44.5258</v>
       </c>
       <c r="G75">
         <v>0.011</v>
@@ -7818,37 +7818,37 @@
         <v>1.525</v>
       </c>
       <c r="M75">
-        <v>10.35730278</v>
+        <v>10.49918364</v>
       </c>
       <c r="N75">
-        <v>-8.832302780000001</v>
+        <v>-8.974183640000001</v>
       </c>
       <c r="O75">
-        <v>-2.208075695</v>
+        <v>-2.24354591</v>
       </c>
       <c r="P75">
-        <v>-6.624227085000001</v>
+        <v>-6.730637730000002</v>
       </c>
       <c r="Q75">
-        <v>-5.789227085000001</v>
+        <v>-5.895637730000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4250149349898634</v>
+        <v>0.4396001247971658</v>
       </c>
       <c r="T75">
-        <v>3.667298248650773</v>
+        <v>3.808348181291188</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03680977645417449</v>
+        <v>0.03631234704263159</v>
       </c>
       <c r="W75">
-        <v>0.2271202547121057</v>
+        <v>0.2272375485673475</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.147239105816698</v>
+        <v>0.1452493881705264</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7864,22 +7864,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2824518183871003</v>
+        <v>0.2843518183871002</v>
       </c>
       <c r="C76">
-        <v>-17.74713659287253</v>
+        <v>-18.56203371212908</v>
       </c>
       <c r="D76">
-        <v>26.76766340712747</v>
+        <v>26.55446628787092</v>
       </c>
       <c r="E76">
-        <v>42.7558</v>
+        <v>43.35749999999999</v>
       </c>
       <c r="F76">
-        <v>44.5258</v>
+        <v>45.1275</v>
       </c>
       <c r="G76">
         <v>0.011</v>
@@ -7900,37 +7900,37 @@
         <v>1.525</v>
       </c>
       <c r="M76">
-        <v>10.49918364</v>
+        <v>10.6410645</v>
       </c>
       <c r="N76">
-        <v>-8.974183640000001</v>
+        <v>-9.1160645</v>
       </c>
       <c r="O76">
-        <v>-2.24354591</v>
+        <v>-2.279016125</v>
       </c>
       <c r="P76">
-        <v>-6.730637730000002</v>
+        <v>-6.837048375</v>
       </c>
       <c r="Q76">
-        <v>-5.895637730000002</v>
+        <v>-6.002048375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4396001247971658</v>
+        <v>0.4553521297890525</v>
       </c>
       <c r="T76">
-        <v>3.808348181291188</v>
+        <v>3.960682108542836</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03631234704263159</v>
+        <v>0.0358281824153965</v>
       </c>
       <c r="W76">
-        <v>0.2272375485673475</v>
+        <v>0.2273517145864495</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1452493881705264</v>
+        <v>0.143312729661586</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7946,22 +7946,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2843518183871002</v>
+        <v>0.2862518183871003</v>
       </c>
       <c r="C77">
-        <v>-18.56203371212908</v>
+        <v>-19.37356155325496</v>
       </c>
       <c r="D77">
-        <v>26.55446628787092</v>
+        <v>26.34463844674504</v>
       </c>
       <c r="E77">
-        <v>43.35749999999999</v>
+        <v>43.9592</v>
       </c>
       <c r="F77">
-        <v>45.1275</v>
+        <v>45.7292</v>
       </c>
       <c r="G77">
         <v>0.011</v>
@@ -7982,37 +7982,37 @@
         <v>1.525</v>
       </c>
       <c r="M77">
-        <v>10.6410645</v>
+        <v>10.78294536</v>
       </c>
       <c r="N77">
-        <v>-9.1160645</v>
+        <v>-9.257945359999999</v>
       </c>
       <c r="O77">
-        <v>-2.279016125</v>
+        <v>-2.31448634</v>
       </c>
       <c r="P77">
-        <v>-6.837048375</v>
+        <v>-6.943459019999999</v>
       </c>
       <c r="Q77">
-        <v>-6.002048375</v>
+        <v>-6.108459019999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4553521297890525</v>
+        <v>0.4724168018635965</v>
       </c>
       <c r="T77">
-        <v>3.960682108542836</v>
+        <v>4.125710529732122</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0358281824153965</v>
+        <v>0.03535675896256234</v>
       </c>
       <c r="W77">
-        <v>0.2273517145864495</v>
+        <v>0.2274628762366278</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.143312729661586</v>
+        <v>0.1414270358502494</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8028,22 +8028,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2862518183871003</v>
+        <v>0.2881518183871002</v>
       </c>
       <c r="C78">
-        <v>-19.37356155325496</v>
+        <v>-20.18179936007621</v>
       </c>
       <c r="D78">
-        <v>26.34463844674504</v>
+        <v>26.13810063992379</v>
       </c>
       <c r="E78">
-        <v>43.9592</v>
+        <v>44.5609</v>
       </c>
       <c r="F78">
-        <v>45.7292</v>
+        <v>46.3309</v>
       </c>
       <c r="G78">
         <v>0.011</v>
@@ -8064,37 +8064,37 @@
         <v>1.525</v>
       </c>
       <c r="M78">
-        <v>10.78294536</v>
+        <v>10.92482622</v>
       </c>
       <c r="N78">
-        <v>-9.257945359999999</v>
+        <v>-9.39982622</v>
       </c>
       <c r="O78">
-        <v>-2.31448634</v>
+        <v>-2.349956555</v>
       </c>
       <c r="P78">
-        <v>-6.943459019999999</v>
+        <v>-7.049869664999999</v>
       </c>
       <c r="Q78">
-        <v>-6.108459019999999</v>
+        <v>-6.214869664999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4724168018635965</v>
+        <v>0.4909653584663615</v>
       </c>
       <c r="T78">
-        <v>4.125710529732122</v>
+        <v>4.305089248416127</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03535675896256234</v>
+        <v>0.03489758027473686</v>
       </c>
       <c r="W78">
-        <v>0.2274628762366278</v>
+        <v>0.227571150571217</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1414270358502494</v>
+        <v>0.1395903210989474</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8110,22 +8110,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2881518183871002</v>
+        <v>0.2900518183871003</v>
       </c>
       <c r="C79">
-        <v>-20.18179936007621</v>
+        <v>-20.98682391071332</v>
       </c>
       <c r="D79">
-        <v>26.13810063992379</v>
+        <v>25.93477608928668</v>
       </c>
       <c r="E79">
-        <v>44.5609</v>
+        <v>45.1626</v>
       </c>
       <c r="F79">
-        <v>46.3309</v>
+        <v>46.9326</v>
       </c>
       <c r="G79">
         <v>0.011</v>
@@ -8146,37 +8146,37 @@
         <v>1.525</v>
       </c>
       <c r="M79">
-        <v>10.92482622</v>
+        <v>11.06670708</v>
       </c>
       <c r="N79">
-        <v>-9.39982622</v>
+        <v>-9.54170708</v>
       </c>
       <c r="O79">
-        <v>-2.349956555</v>
+        <v>-2.38542677</v>
       </c>
       <c r="P79">
-        <v>-7.049869664999999</v>
+        <v>-7.15628031</v>
       </c>
       <c r="Q79">
-        <v>-6.214869664999999</v>
+        <v>-6.32128031</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4909653584663615</v>
+        <v>0.5112001474875597</v>
       </c>
       <c r="T79">
-        <v>4.305089248416127</v>
+        <v>4.500775123344132</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03489758027473686</v>
+        <v>0.03445017539941971</v>
       </c>
       <c r="W79">
-        <v>0.227571150571217</v>
+        <v>0.2276766486408168</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1395903210989474</v>
+        <v>0.1378007015976789</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8192,22 +8192,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2900518183871003</v>
+        <v>0.2919518183871003</v>
       </c>
       <c r="C80">
-        <v>-20.98682391071332</v>
+        <v>-21.78870961274277</v>
       </c>
       <c r="D80">
-        <v>25.93477608928668</v>
+        <v>25.73459038725724</v>
       </c>
       <c r="E80">
-        <v>45.1626</v>
+        <v>45.7643</v>
       </c>
       <c r="F80">
-        <v>46.9326</v>
+        <v>47.5343</v>
       </c>
       <c r="G80">
         <v>0.011</v>
@@ -8228,37 +8228,37 @@
         <v>1.525</v>
       </c>
       <c r="M80">
-        <v>11.06670708</v>
+        <v>11.20858794</v>
       </c>
       <c r="N80">
-        <v>-9.54170708</v>
+        <v>-9.683587940000001</v>
       </c>
       <c r="O80">
-        <v>-2.38542677</v>
+        <v>-2.420896985</v>
       </c>
       <c r="P80">
-        <v>-7.15628031</v>
+        <v>-7.262690955</v>
       </c>
       <c r="Q80">
-        <v>-6.32128031</v>
+        <v>-6.427690955</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5112001474875597</v>
+        <v>0.5333620592726817</v>
       </c>
       <c r="T80">
-        <v>4.500775123344132</v>
+        <v>4.715097748265282</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03445017539941971</v>
+        <v>0.03401409722980681</v>
       </c>
       <c r="W80">
-        <v>0.2276766486408168</v>
+        <v>0.2277794758732115</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1378007015976789</v>
+        <v>0.1360563889192272</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8274,22 +8274,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2919518183871003</v>
+        <v>0.2938518183871002</v>
       </c>
       <c r="C81">
-        <v>-21.78870961274277</v>
+        <v>-22.58752859398516</v>
       </c>
       <c r="D81">
-        <v>25.73459038725724</v>
+        <v>25.53747140601484</v>
       </c>
       <c r="E81">
-        <v>45.7643</v>
+        <v>46.366</v>
       </c>
       <c r="F81">
-        <v>47.5343</v>
+        <v>48.136</v>
       </c>
       <c r="G81">
         <v>0.011</v>
@@ -8310,37 +8310,37 @@
         <v>1.525</v>
       </c>
       <c r="M81">
-        <v>11.20858794</v>
+        <v>11.3504688</v>
       </c>
       <c r="N81">
-        <v>-9.683587940000001</v>
+        <v>-9.825468800000001</v>
       </c>
       <c r="O81">
-        <v>-2.420896985</v>
+        <v>-2.4563672</v>
       </c>
       <c r="P81">
-        <v>-7.262690955</v>
+        <v>-7.3691016</v>
       </c>
       <c r="Q81">
-        <v>-6.427690955</v>
+        <v>-6.534101600000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5333620592726817</v>
+        <v>0.5577401622363156</v>
       </c>
       <c r="T81">
-        <v>4.715097748265282</v>
+        <v>4.950852635678546</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03401409722980681</v>
+        <v>0.03358892101443422</v>
       </c>
       <c r="W81">
-        <v>0.2277794758732115</v>
+        <v>0.2278797324247964</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1360563889192272</v>
+        <v>0.1343556840577369</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8356,22 +8356,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2938518183871002</v>
+        <v>0.2957518183871003</v>
       </c>
       <c r="C82">
-        <v>-22.58752859398516</v>
+        <v>-23.38335078915273</v>
       </c>
       <c r="D82">
-        <v>25.53747140601484</v>
+        <v>25.34334921084728</v>
       </c>
       <c r="E82">
-        <v>46.366</v>
+        <v>46.9677</v>
       </c>
       <c r="F82">
-        <v>48.136</v>
+        <v>48.7377</v>
       </c>
       <c r="G82">
         <v>0.011</v>
@@ -8392,37 +8392,37 @@
         <v>1.525</v>
       </c>
       <c r="M82">
-        <v>11.3504688</v>
+        <v>11.49234966</v>
       </c>
       <c r="N82">
-        <v>-9.825468800000001</v>
+        <v>-9.967349660000002</v>
       </c>
       <c r="O82">
-        <v>-2.4563672</v>
+        <v>-2.491837415</v>
       </c>
       <c r="P82">
-        <v>-7.3691016</v>
+        <v>-7.475512245000001</v>
       </c>
       <c r="Q82">
-        <v>-6.534101600000001</v>
+        <v>-6.640512245000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5577401622363156</v>
+        <v>0.584684381301385</v>
       </c>
       <c r="T82">
-        <v>4.950852635678546</v>
+        <v>5.211423827030049</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03358892101443422</v>
+        <v>0.03317424297721898</v>
       </c>
       <c r="W82">
-        <v>0.2278797324247964</v>
+        <v>0.2279775135059718</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1343556840577369</v>
+        <v>0.132696971908876</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8438,22 +8438,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2957518183871003</v>
+        <v>0.2976518183871003</v>
       </c>
       <c r="C83">
-        <v>-23.38335078915273</v>
+        <v>-24.17624402257461</v>
       </c>
       <c r="D83">
-        <v>25.34334921084728</v>
+        <v>25.1521559774254</v>
       </c>
       <c r="E83">
-        <v>46.9677</v>
+        <v>47.5694</v>
       </c>
       <c r="F83">
-        <v>48.7377</v>
+        <v>49.3394</v>
       </c>
       <c r="G83">
         <v>0.011</v>
@@ -8474,37 +8474,37 @@
         <v>1.525</v>
       </c>
       <c r="M83">
-        <v>11.49234966</v>
+        <v>11.63423052</v>
       </c>
       <c r="N83">
-        <v>-9.967349660000002</v>
+        <v>-10.10923052</v>
       </c>
       <c r="O83">
-        <v>-2.491837415</v>
+        <v>-2.52730763</v>
       </c>
       <c r="P83">
-        <v>-7.475512245000001</v>
+        <v>-7.58192289</v>
       </c>
       <c r="Q83">
-        <v>-6.640512245000001</v>
+        <v>-6.74692289</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.584684381301385</v>
+        <v>0.6146224024847953</v>
       </c>
       <c r="T83">
-        <v>5.211423827030049</v>
+        <v>5.500947372976163</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03317424297721898</v>
+        <v>0.03276967903847241</v>
       </c>
       <c r="W83">
-        <v>0.2279775135059718</v>
+        <v>0.2280729096827282</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.132696971908876</v>
+        <v>0.1310787161538897</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8520,22 +8520,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2976518183871003</v>
+        <v>0.2995518183871003</v>
       </c>
       <c r="C84">
-        <v>-24.17624402257461</v>
+        <v>-24.96627408720573</v>
       </c>
       <c r="D84">
-        <v>25.1521559774254</v>
+        <v>24.96382591279427</v>
       </c>
       <c r="E84">
-        <v>47.5694</v>
+        <v>48.1711</v>
       </c>
       <c r="F84">
-        <v>49.3394</v>
+        <v>49.94110000000001</v>
       </c>
       <c r="G84">
         <v>0.011</v>
@@ -8556,37 +8556,37 @@
         <v>1.525</v>
       </c>
       <c r="M84">
-        <v>11.63423052</v>
+        <v>11.77611138</v>
       </c>
       <c r="N84">
-        <v>-10.10923052</v>
+        <v>-10.25111138</v>
       </c>
       <c r="O84">
-        <v>-2.52730763</v>
+        <v>-2.562777845</v>
       </c>
       <c r="P84">
-        <v>-7.58192289</v>
+        <v>-7.688333535000001</v>
       </c>
       <c r="Q84">
-        <v>-6.74692289</v>
+        <v>-6.853333535000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6146224024847953</v>
+        <v>0.6480825438074304</v>
       </c>
       <c r="T84">
-        <v>5.500947372976163</v>
+        <v>5.824532512562997</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03276967903847241</v>
+        <v>0.03237486362837033</v>
       </c>
       <c r="W84">
-        <v>0.2280729096827282</v>
+        <v>0.2281660071564303</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1310787161538897</v>
+        <v>0.1294994545134813</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8602,22 +8602,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2995518183871003</v>
+        <v>0.3014518183871003</v>
       </c>
       <c r="C85">
-        <v>-24.96627408720573</v>
+        <v>-25.75350482011251</v>
       </c>
       <c r="D85">
-        <v>24.96382591279427</v>
+        <v>24.7782951798875</v>
       </c>
       <c r="E85">
-        <v>48.1711</v>
+        <v>48.7728</v>
       </c>
       <c r="F85">
-        <v>49.94110000000001</v>
+        <v>50.54280000000001</v>
       </c>
       <c r="G85">
         <v>0.011</v>
@@ -8638,37 +8638,37 @@
         <v>1.525</v>
       </c>
       <c r="M85">
-        <v>11.77611138</v>
+        <v>11.91799224</v>
       </c>
       <c r="N85">
-        <v>-10.25111138</v>
+        <v>-10.39299224</v>
       </c>
       <c r="O85">
-        <v>-2.562777845</v>
+        <v>-2.59824806</v>
       </c>
       <c r="P85">
-        <v>-7.688333535000001</v>
+        <v>-7.794744180000001</v>
       </c>
       <c r="Q85">
-        <v>-6.853333535000001</v>
+        <v>-6.959744180000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6480825438074304</v>
+        <v>0.6857252027953948</v>
       </c>
       <c r="T85">
-        <v>5.824532512562997</v>
+        <v>6.188565794598185</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03237486362837033</v>
+        <v>0.03198944858517545</v>
       </c>
       <c r="W85">
-        <v>0.2281660071564303</v>
+        <v>0.2282568880236156</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1294994545134813</v>
+        <v>0.1279577943407018</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8684,22 +8684,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3014518183871002</v>
+        <v>0.3033518183871002</v>
       </c>
       <c r="C86">
-        <v>-25.7535048201125</v>
+        <v>-26.5379981746173</v>
       </c>
       <c r="D86">
-        <v>24.7782951798875</v>
+        <v>24.5955018253827</v>
       </c>
       <c r="E86">
-        <v>48.7728</v>
+        <v>49.3745</v>
       </c>
       <c r="F86">
-        <v>50.5428</v>
+        <v>51.1445</v>
       </c>
       <c r="G86">
         <v>0.011</v>
@@ -8720,37 +8720,37 @@
         <v>1.525</v>
       </c>
       <c r="M86">
-        <v>11.91799224</v>
+        <v>12.0598731</v>
       </c>
       <c r="N86">
-        <v>-10.39299224</v>
+        <v>-10.5348731</v>
       </c>
       <c r="O86">
-        <v>-2.59824806</v>
+        <v>-2.633718275</v>
       </c>
       <c r="P86">
-        <v>-7.79474418</v>
+        <v>-7.901154825000001</v>
       </c>
       <c r="Q86">
-        <v>-6.95974418</v>
+        <v>-7.066154825000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6857252027953943</v>
+        <v>0.728386882981754</v>
       </c>
       <c r="T86">
-        <v>6.18856579459818</v>
+        <v>6.601136847571392</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03198944858517545</v>
+        <v>0.0316131021312322</v>
       </c>
       <c r="W86">
-        <v>0.2282568880236156</v>
+        <v>0.2283456305174554</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1279577943407019</v>
+        <v>0.1264524085249289</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8766,22 +8766,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3033518183871002</v>
+        <v>0.3052518183871002</v>
       </c>
       <c r="C87">
-        <v>-26.5379981746173</v>
+        <v>-27.31981428927294</v>
       </c>
       <c r="D87">
-        <v>24.5955018253827</v>
+        <v>24.41538571072706</v>
       </c>
       <c r="E87">
-        <v>49.3745</v>
+        <v>49.9762</v>
       </c>
       <c r="F87">
-        <v>51.1445</v>
+        <v>51.7462</v>
       </c>
       <c r="G87">
         <v>0.011</v>
@@ -8802,37 +8802,37 @@
         <v>1.525</v>
       </c>
       <c r="M87">
-        <v>12.0598731</v>
+        <v>12.20175396</v>
       </c>
       <c r="N87">
-        <v>-10.5348731</v>
+        <v>-10.67675396</v>
       </c>
       <c r="O87">
-        <v>-2.633718275</v>
+        <v>-2.66918849</v>
       </c>
       <c r="P87">
-        <v>-7.901154825000001</v>
+        <v>-8.007565470000001</v>
       </c>
       <c r="Q87">
-        <v>-7.066154825000001</v>
+        <v>-7.172565470000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.728386882981754</v>
+        <v>0.7771430889090222</v>
       </c>
       <c r="T87">
-        <v>6.601136847571392</v>
+        <v>7.072646622397921</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0316131021312322</v>
+        <v>0.03124550792040392</v>
       </c>
       <c r="W87">
-        <v>0.2283456305174554</v>
+        <v>0.2284323092323688</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1264524085249289</v>
+        <v>0.1249820316816157</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8848,22 +8848,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3052518183871002</v>
+        <v>0.3071518183871003</v>
       </c>
       <c r="C88">
-        <v>-27.31981428927294</v>
+        <v>-28.09901155382869</v>
       </c>
       <c r="D88">
-        <v>24.41538571072706</v>
+        <v>24.23788844617131</v>
       </c>
       <c r="E88">
-        <v>49.9762</v>
+        <v>50.5779</v>
       </c>
       <c r="F88">
-        <v>51.7462</v>
+        <v>52.3479</v>
       </c>
       <c r="G88">
         <v>0.011</v>
@@ -8884,37 +8884,37 @@
         <v>1.525</v>
       </c>
       <c r="M88">
-        <v>12.20175396</v>
+        <v>12.34363482</v>
       </c>
       <c r="N88">
-        <v>-10.67675396</v>
+        <v>-10.81863482</v>
       </c>
       <c r="O88">
-        <v>-2.66918849</v>
+        <v>-2.704658705</v>
       </c>
       <c r="P88">
-        <v>-8.007565470000001</v>
+        <v>-8.113976115000002</v>
       </c>
       <c r="Q88">
-        <v>-7.172565470000001</v>
+        <v>-7.278976115000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7771430889090222</v>
+        <v>0.8334002495943317</v>
       </c>
       <c r="T88">
-        <v>7.072646622397921</v>
+        <v>7.616696362582377</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03124550792040392</v>
+        <v>0.03088636415120388</v>
       </c>
       <c r="W88">
-        <v>0.2284323092323688</v>
+        <v>0.2285169953331462</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1249820316816157</v>
+        <v>0.1235454566048155</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8930,22 +8930,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3071518183871003</v>
+        <v>0.3090518183871003</v>
       </c>
       <c r="C89">
-        <v>-28.09901155382869</v>
+        <v>-28.87564667233948</v>
       </c>
       <c r="D89">
-        <v>24.23788844617131</v>
+        <v>24.06295332766052</v>
       </c>
       <c r="E89">
-        <v>50.5779</v>
+        <v>51.1796</v>
       </c>
       <c r="F89">
-        <v>52.3479</v>
+        <v>52.9496</v>
       </c>
       <c r="G89">
         <v>0.011</v>
@@ -8966,37 +8966,37 @@
         <v>1.525</v>
       </c>
       <c r="M89">
-        <v>12.34363482</v>
+        <v>12.48551568</v>
       </c>
       <c r="N89">
-        <v>-10.81863482</v>
+        <v>-10.96051568</v>
       </c>
       <c r="O89">
-        <v>-2.704658705</v>
+        <v>-2.74012892</v>
       </c>
       <c r="P89">
-        <v>-8.113976115000002</v>
+        <v>-8.22038676</v>
       </c>
       <c r="Q89">
-        <v>-7.278976115000002</v>
+        <v>-7.38538676</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8334002495943317</v>
+        <v>0.8990336037271929</v>
       </c>
       <c r="T89">
-        <v>7.616696362582377</v>
+        <v>8.251421059464244</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03088636415120388</v>
+        <v>0.03053538274039475</v>
       </c>
       <c r="W89">
-        <v>0.2285169953331462</v>
+        <v>0.2285997567498149</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1235454566048155</v>
+        <v>0.122141530961579</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9012,22 +9012,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3090518183871003</v>
+        <v>0.3109518183871003</v>
       </c>
       <c r="C90">
-        <v>-28.87564667233948</v>
+        <v>-29.64977472356184</v>
       </c>
       <c r="D90">
-        <v>24.06295332766052</v>
+        <v>23.89052527643816</v>
       </c>
       <c r="E90">
-        <v>51.1796</v>
+        <v>51.7813</v>
       </c>
       <c r="F90">
-        <v>52.9496</v>
+        <v>53.5513</v>
       </c>
       <c r="G90">
         <v>0.011</v>
@@ -9048,37 +9048,37 @@
         <v>1.525</v>
       </c>
       <c r="M90">
-        <v>12.48551568</v>
+        <v>12.62739654</v>
       </c>
       <c r="N90">
-        <v>-10.96051568</v>
+        <v>-11.10239654</v>
       </c>
       <c r="O90">
-        <v>-2.74012892</v>
+        <v>-2.775599135</v>
       </c>
       <c r="P90">
-        <v>-8.22038676</v>
+        <v>-8.326797405000001</v>
       </c>
       <c r="Q90">
-        <v>-7.38538676</v>
+        <v>-7.491797405000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8990336037271929</v>
+        <v>0.9766002949751194</v>
       </c>
       <c r="T90">
-        <v>8.251421059464244</v>
+        <v>9.001550246688264</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03053538274039475</v>
+        <v>0.03019228855230042</v>
       </c>
       <c r="W90">
-        <v>0.2285997567498149</v>
+        <v>0.2286806583593676</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.122141530961579</v>
+        <v>0.1207691542092018</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9094,22 +9094,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3109518183871003</v>
+        <v>0.3128518183871002</v>
       </c>
       <c r="C91">
-        <v>-29.64977472356184</v>
+        <v>-30.42144921877174</v>
       </c>
       <c r="D91">
-        <v>23.89052527643816</v>
+        <v>23.72055078122827</v>
       </c>
       <c r="E91">
-        <v>51.7813</v>
+        <v>52.383</v>
       </c>
       <c r="F91">
-        <v>53.5513</v>
+        <v>54.15300000000001</v>
       </c>
       <c r="G91">
         <v>0.011</v>
@@ -9130,37 +9130,37 @@
         <v>1.525</v>
       </c>
       <c r="M91">
-        <v>12.62739654</v>
+        <v>12.7692774</v>
       </c>
       <c r="N91">
-        <v>-11.10239654</v>
+        <v>-11.2442774</v>
       </c>
       <c r="O91">
-        <v>-2.775599135</v>
+        <v>-2.81106935</v>
       </c>
       <c r="P91">
-        <v>-8.326797405000001</v>
+        <v>-8.433208050000001</v>
       </c>
       <c r="Q91">
-        <v>-7.491797405000001</v>
+        <v>-7.598208050000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9766002949751194</v>
+        <v>1.069680324472631</v>
       </c>
       <c r="T91">
-        <v>9.001550246688264</v>
+        <v>9.901705271357091</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03019228855230042</v>
+        <v>0.02985681867949708</v>
       </c>
       <c r="W91">
-        <v>0.2286806583593676</v>
+        <v>0.2287597621553746</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1207691542092018</v>
+        <v>0.1194272747179883</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9176,22 +9176,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3128518183871002</v>
+        <v>0.3147518183871003</v>
       </c>
       <c r="C92">
-        <v>-30.42144921877174</v>
+        <v>-31.19072215713154</v>
       </c>
       <c r="D92">
-        <v>23.72055078122827</v>
+        <v>23.55297784286847</v>
       </c>
       <c r="E92">
-        <v>52.383</v>
+        <v>52.9847</v>
       </c>
       <c r="F92">
-        <v>54.15300000000001</v>
+        <v>54.75470000000001</v>
       </c>
       <c r="G92">
         <v>0.011</v>
@@ -9212,37 +9212,37 @@
         <v>1.525</v>
       </c>
       <c r="M92">
-        <v>12.7692774</v>
+        <v>12.91115826</v>
       </c>
       <c r="N92">
-        <v>-11.2442774</v>
+        <v>-11.38615826</v>
       </c>
       <c r="O92">
-        <v>-2.81106935</v>
+        <v>-2.846539565</v>
       </c>
       <c r="P92">
-        <v>-8.433208050000001</v>
+        <v>-8.539618695000001</v>
       </c>
       <c r="Q92">
-        <v>-7.598208050000001</v>
+        <v>-7.704618695000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.069680324472631</v>
+        <v>1.183444804969591</v>
       </c>
       <c r="T92">
-        <v>9.901705271357091</v>
+        <v>11.00189474595233</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02985681867949708</v>
+        <v>0.02952872177093118</v>
       </c>
       <c r="W92">
-        <v>0.2287597621553746</v>
+        <v>0.2288371274064145</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1194272747179883</v>
+        <v>0.1181148870837248</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9258,22 +9258,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3147518183871003</v>
+        <v>0.3166518183871003</v>
       </c>
       <c r="C93">
-        <v>-31.19072215713154</v>
+        <v>-31.95764407872665</v>
       </c>
       <c r="D93">
-        <v>23.55297784286847</v>
+        <v>23.38775592127335</v>
       </c>
       <c r="E93">
-        <v>52.9847</v>
+        <v>53.5864</v>
       </c>
       <c r="F93">
-        <v>54.75470000000001</v>
+        <v>55.3564</v>
       </c>
       <c r="G93">
         <v>0.011</v>
@@ -9294,37 +9294,37 @@
         <v>1.525</v>
       </c>
       <c r="M93">
-        <v>12.91115826</v>
+        <v>13.05303912</v>
       </c>
       <c r="N93">
-        <v>-11.38615826</v>
+        <v>-11.52803912</v>
       </c>
       <c r="O93">
-        <v>-2.846539565</v>
+        <v>-2.88200978</v>
       </c>
       <c r="P93">
-        <v>-8.539618695000001</v>
+        <v>-8.64602934</v>
       </c>
       <c r="Q93">
-        <v>-7.704618695000002</v>
+        <v>-7.81102934</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.183444804969591</v>
+        <v>1.32565040559079</v>
       </c>
       <c r="T93">
-        <v>11.00189474595233</v>
+        <v>12.37713158919637</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02952872177093118</v>
+        <v>0.02920775740385584</v>
       </c>
       <c r="W93">
-        <v>0.2288371274064145</v>
+        <v>0.2289128108041708</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1181148870837248</v>
+        <v>0.1168310296154234</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9340,22 +9340,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3166518183871003</v>
+        <v>0.3185518183871003</v>
       </c>
       <c r="C94">
-        <v>-31.95764407872665</v>
+        <v>-32.72226411538558</v>
       </c>
       <c r="D94">
-        <v>23.38775592127335</v>
+        <v>23.22483588461441</v>
       </c>
       <c r="E94">
-        <v>53.5864</v>
+        <v>54.1881</v>
       </c>
       <c r="F94">
-        <v>55.3564</v>
+        <v>55.9581</v>
       </c>
       <c r="G94">
         <v>0.011</v>
@@ -9376,37 +9376,37 @@
         <v>1.525</v>
       </c>
       <c r="M94">
-        <v>13.05303912</v>
+        <v>13.19491998</v>
       </c>
       <c r="N94">
-        <v>-11.52803912</v>
+        <v>-11.66991998</v>
       </c>
       <c r="O94">
-        <v>-2.88200978</v>
+        <v>-2.917479995</v>
       </c>
       <c r="P94">
-        <v>-8.64602934</v>
+        <v>-8.752439985000001</v>
       </c>
       <c r="Q94">
-        <v>-7.81102934</v>
+        <v>-7.917439985000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.32565040559079</v>
+        <v>1.508486177818046</v>
       </c>
       <c r="T94">
-        <v>12.37713158919637</v>
+        <v>14.14529324479585</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02920775740385584</v>
+        <v>0.0288936954962875</v>
       </c>
       <c r="W94">
-        <v>0.2289128108041708</v>
+        <v>0.2289868666019754</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1168310296154234</v>
+        <v>0.11557478198515</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9422,22 +9422,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3185518183871003</v>
+        <v>0.3204518183871003</v>
       </c>
       <c r="C95">
-        <v>-32.72226411538558</v>
+        <v>-33.48463003939041</v>
       </c>
       <c r="D95">
-        <v>23.22483588461441</v>
+        <v>23.06416996060959</v>
       </c>
       <c r="E95">
-        <v>54.1881</v>
+        <v>54.7898</v>
       </c>
       <c r="F95">
-        <v>55.9581</v>
+        <v>56.5598</v>
       </c>
       <c r="G95">
         <v>0.011</v>
@@ -9458,37 +9458,37 @@
         <v>1.525</v>
       </c>
       <c r="M95">
-        <v>13.19491998</v>
+        <v>13.33680084</v>
       </c>
       <c r="N95">
-        <v>-11.66991998</v>
+        <v>-11.81180084</v>
       </c>
       <c r="O95">
-        <v>-2.917479995</v>
+        <v>-2.95295021</v>
       </c>
       <c r="P95">
-        <v>-8.752439985000001</v>
+        <v>-8.858850629999999</v>
       </c>
       <c r="Q95">
-        <v>-7.917439985000001</v>
+        <v>-8.023850629999998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.508486177818046</v>
+        <v>1.752267207454387</v>
       </c>
       <c r="T95">
-        <v>14.14529324479585</v>
+        <v>16.5028421189285</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0288936954962875</v>
+        <v>0.02858631575696529</v>
       </c>
       <c r="W95">
-        <v>0.2289868666019754</v>
+        <v>0.2290593467445076</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.11557478198515</v>
+        <v>0.1143452630278612</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9504,22 +9504,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3204518183871003</v>
+        <v>0.3223518183871003</v>
       </c>
       <c r="C96">
-        <v>-33.48463003939041</v>
+        <v>-34.24478831017935</v>
       </c>
       <c r="D96">
-        <v>23.06416996060959</v>
+        <v>22.90571168982065</v>
       </c>
       <c r="E96">
-        <v>54.7898</v>
+        <v>55.3915</v>
       </c>
       <c r="F96">
-        <v>56.5598</v>
+        <v>57.1615</v>
       </c>
       <c r="G96">
         <v>0.011</v>
@@ -9540,37 +9540,37 @@
         <v>1.525</v>
       </c>
       <c r="M96">
-        <v>13.33680084</v>
+        <v>13.4786817</v>
       </c>
       <c r="N96">
-        <v>-11.81180084</v>
+        <v>-11.9536817</v>
       </c>
       <c r="O96">
-        <v>-2.95295021</v>
+        <v>-2.988420425</v>
       </c>
       <c r="P96">
-        <v>-8.858850629999999</v>
+        <v>-8.965261275</v>
       </c>
       <c r="Q96">
-        <v>-8.023850629999998</v>
+        <v>-8.130261274999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.752267207454387</v>
+        <v>2.093560648945266</v>
       </c>
       <c r="T96">
-        <v>16.5028421189285</v>
+        <v>19.80341054271421</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02858631575696529</v>
+        <v>0.02828540717004987</v>
       </c>
       <c r="W96">
-        <v>0.2290593467445076</v>
+        <v>0.2291303009893022</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1143452630278612</v>
+        <v>0.1131416286801995</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9586,22 +9586,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3223518183871003</v>
+        <v>0.3242518183871003</v>
       </c>
       <c r="C97">
-        <v>-34.24478831017935</v>
+        <v>-35.00278411913743</v>
       </c>
       <c r="D97">
-        <v>22.90571168982065</v>
+        <v>22.74941588086257</v>
       </c>
       <c r="E97">
-        <v>55.3915</v>
+        <v>55.9932</v>
       </c>
       <c r="F97">
-        <v>57.1615</v>
+        <v>57.7632</v>
       </c>
       <c r="G97">
         <v>0.011</v>
@@ -9622,37 +9622,37 @@
         <v>1.525</v>
       </c>
       <c r="M97">
-        <v>13.4786817</v>
+        <v>13.62056256</v>
       </c>
       <c r="N97">
-        <v>-11.9536817</v>
+        <v>-12.09556256</v>
       </c>
       <c r="O97">
-        <v>-2.988420425</v>
+        <v>-3.02389064</v>
       </c>
       <c r="P97">
-        <v>-8.965261275</v>
+        <v>-9.07167192</v>
       </c>
       <c r="Q97">
-        <v>-8.130261274999999</v>
+        <v>-8.236671919999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.093560648945266</v>
+        <v>2.605500811181583</v>
       </c>
       <c r="T97">
-        <v>19.80341054271421</v>
+        <v>24.75426317839277</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02828540717004987</v>
+        <v>0.02799076751202851</v>
       </c>
       <c r="W97">
-        <v>0.2291303009893022</v>
+        <v>0.2291997770206637</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1131416286801995</v>
+        <v>0.1119630700481141</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9668,22 +9668,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3242518183871003</v>
+        <v>0.3261518183871003</v>
       </c>
       <c r="C98">
-        <v>-35.00278411913742</v>
+        <v>-35.75866143256565</v>
       </c>
       <c r="D98">
-        <v>22.74941588086257</v>
+        <v>22.59523856743436</v>
       </c>
       <c r="E98">
-        <v>55.99319999999999</v>
+        <v>56.5949</v>
       </c>
       <c r="F98">
-        <v>57.7632</v>
+        <v>58.3649</v>
       </c>
       <c r="G98">
         <v>0.011</v>
@@ -9704,37 +9704,37 @@
         <v>1.525</v>
       </c>
       <c r="M98">
-        <v>13.62056256</v>
+        <v>13.76244342</v>
       </c>
       <c r="N98">
-        <v>-12.09556256</v>
+        <v>-12.23744342</v>
       </c>
       <c r="O98">
-        <v>-3.02389064</v>
+        <v>-3.059360855</v>
       </c>
       <c r="P98">
-        <v>-9.07167192</v>
+        <v>-9.178082565</v>
       </c>
       <c r="Q98">
-        <v>-8.236671919999999</v>
+        <v>-8.343082565</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.605500811181575</v>
+        <v>3.458734414908769</v>
       </c>
       <c r="T98">
-        <v>24.7542631783927</v>
+        <v>33.00568423785695</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02799076751202852</v>
+        <v>0.02770220289850245</v>
       </c>
       <c r="W98">
-        <v>0.2291997770206637</v>
+        <v>0.2292678205565331</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1119630700481141</v>
+        <v>0.1108088115940098</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9750,22 +9750,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3261518183871003</v>
+        <v>0.3280518183871003</v>
       </c>
       <c r="C99">
-        <v>-35.75866143256565</v>
+        <v>-36.51246303291476</v>
       </c>
       <c r="D99">
-        <v>22.59523856743436</v>
+        <v>22.44313696708524</v>
       </c>
       <c r="E99">
-        <v>56.5949</v>
+        <v>57.1966</v>
       </c>
       <c r="F99">
-        <v>58.3649</v>
+        <v>58.9666</v>
       </c>
       <c r="G99">
         <v>0.011</v>
@@ -9786,37 +9786,37 @@
         <v>1.525</v>
       </c>
       <c r="M99">
-        <v>13.76244342</v>
+        <v>13.90432428</v>
       </c>
       <c r="N99">
-        <v>-12.23744342</v>
+        <v>-12.37932428</v>
       </c>
       <c r="O99">
-        <v>-3.059360855</v>
+        <v>-3.09483107</v>
       </c>
       <c r="P99">
-        <v>-9.178082565</v>
+        <v>-9.284493210000001</v>
       </c>
       <c r="Q99">
-        <v>-8.343082565</v>
+        <v>-8.44949321</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.458734414908769</v>
+        <v>5.165201622363152</v>
       </c>
       <c r="T99">
-        <v>33.00568423785695</v>
+        <v>49.50852635678541</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02770220289850245</v>
+        <v>0.02741952735872181</v>
       </c>
       <c r="W99">
-        <v>0.2292678205565331</v>
+        <v>0.2293344754488134</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1108088115940098</v>
+        <v>0.1096781094348873</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9832,22 +9832,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3280518183871003</v>
+        <v>0.3299518183871002</v>
       </c>
       <c r="C100">
-        <v>-36.51246303291476</v>
+        <v>-37.26423055836473</v>
       </c>
       <c r="D100">
-        <v>22.44313696708524</v>
+        <v>22.29306944163527</v>
       </c>
       <c r="E100">
-        <v>57.1966</v>
+        <v>57.7983</v>
       </c>
       <c r="F100">
-        <v>58.9666</v>
+        <v>59.5683</v>
       </c>
       <c r="G100">
         <v>0.011</v>
@@ -9868,37 +9868,37 @@
         <v>1.525</v>
       </c>
       <c r="M100">
-        <v>13.90432428</v>
+        <v>14.04620514</v>
       </c>
       <c r="N100">
-        <v>-12.37932428</v>
+        <v>-12.52120514</v>
       </c>
       <c r="O100">
-        <v>-3.09483107</v>
+        <v>-3.130301285</v>
       </c>
       <c r="P100">
-        <v>-9.284493210000001</v>
+        <v>-9.390903855000001</v>
       </c>
       <c r="Q100">
-        <v>-8.44949321</v>
+        <v>-8.555903855</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.165201622363152</v>
+        <v>10.2846032447263</v>
       </c>
       <c r="T100">
-        <v>49.50852635678541</v>
+        <v>99.01705271357082</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02741952735872181</v>
+        <v>0.02714256243590644</v>
       </c>
       <c r="W100">
-        <v>0.2293344754488134</v>
+        <v>0.2293997837776133</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9906,91 +9906,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1096781094348873</v>
+        <v>0.1085702497436258</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3299518183871002</v>
-      </c>
-      <c r="C101">
-        <v>-37.26423055836473</v>
-      </c>
-      <c r="D101">
-        <v>22.29306944163527</v>
-      </c>
-      <c r="E101">
-        <v>57.7983</v>
-      </c>
-      <c r="F101">
-        <v>59.5683</v>
-      </c>
-      <c r="G101">
-        <v>0.011</v>
-      </c>
-      <c r="H101">
-        <v>58.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.36</v>
-      </c>
-      <c r="K101">
-        <v>0.835</v>
-      </c>
-      <c r="L101">
-        <v>1.525</v>
-      </c>
-      <c r="M101">
-        <v>14.04620514</v>
-      </c>
-      <c r="N101">
-        <v>-12.52120514</v>
-      </c>
-      <c r="O101">
-        <v>-3.130301285</v>
-      </c>
-      <c r="P101">
-        <v>-9.390903855000001</v>
-      </c>
-      <c r="Q101">
-        <v>-8.555903855</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.2846032447263</v>
-      </c>
-      <c r="T101">
-        <v>99.01705271357082</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02714256243590644</v>
-      </c>
-      <c r="W101">
-        <v>0.2293997837776133</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1085702497436258</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
